--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3107,12 +3107,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Multinivel</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>MULTINIVEL (sin agencia)</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE OTAVALO</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 3</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANGOLQUI</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4267,12 +4267,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4367,12 +4367,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4452,20 +4452,40 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Sin respuestas</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
           <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
-      <c r="C192" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D192"/>
+  <autoFilter ref="A1:D193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,13 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -63,18 +70,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -437,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -516,8 +526,57 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:53</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>César Izquierdo</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CUENCA</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>@cdizquierdoc</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2072,7 +2131,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2092,7 +2151,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2112,7 +2171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2132,7 +2191,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2152,7 +2211,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2172,7 +2231,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2192,7 +2251,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2212,7 +2271,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2232,7 +2291,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2252,7 +2311,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2272,7 +2331,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2292,7 +2351,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2312,7 +2371,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2332,7 +2391,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2352,7 +2411,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2372,7 +2431,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2392,7 +2451,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2412,7 +2471,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2432,7 +2491,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2452,7 +2511,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2472,7 +2531,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2492,7 +2551,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2512,7 +2571,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2532,7 +2591,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2552,7 +2611,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2572,7 +2631,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2592,7 +2651,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2612,7 +2671,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2632,7 +2691,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2652,7 +2711,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2672,7 +2731,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2692,7 +2751,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2712,7 +2771,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2732,7 +2791,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2752,7 +2811,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2767,12 +2826,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2792,7 +2851,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2812,7 +2871,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2832,7 +2891,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2852,7 +2911,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2872,7 +2931,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2892,7 +2951,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2912,7 +2971,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2932,7 +2991,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2952,7 +3011,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2972,7 +3031,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2992,7 +3051,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3012,7 +3071,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3032,7 +3091,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3052,7 +3111,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3072,7 +3131,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3087,12 +3146,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Multinivel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>MULTINIVEL (sin agencia)</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3107,12 +3166,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Multinivel</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MULTINIVEL (sin agencia)</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3132,7 +3191,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3152,7 +3211,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3172,7 +3231,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3192,7 +3251,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3212,7 +3271,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3232,7 +3291,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3252,7 +3311,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3272,7 +3331,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3292,7 +3351,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3312,7 +3371,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3332,7 +3391,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3352,7 +3411,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3372,7 +3431,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3392,7 +3451,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3412,7 +3471,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3432,7 +3491,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3452,7 +3511,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3472,7 +3531,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3492,7 +3551,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3512,7 +3571,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3532,7 +3591,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3552,7 +3611,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3572,7 +3631,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -3592,7 +3651,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3612,7 +3671,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3632,7 +3691,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3652,7 +3711,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3672,7 +3731,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3692,7 +3751,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -3712,7 +3771,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -3732,7 +3791,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -3752,7 +3811,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3772,7 +3831,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3792,7 +3851,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3812,7 +3871,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -3832,7 +3891,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3852,7 +3911,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3872,7 +3931,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3892,7 +3951,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE OTAVALO</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3912,7 +3971,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3932,7 +3991,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3952,7 +4011,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3972,7 +4031,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3992,7 +4051,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4012,7 +4071,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -4032,7 +4091,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4052,7 +4111,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4072,7 +4131,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 3</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4092,7 +4151,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -4112,7 +4171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4132,7 +4191,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -4152,7 +4211,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANGOLQUI</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4172,7 +4231,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4192,7 +4251,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4212,7 +4271,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4232,7 +4291,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4252,7 +4311,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4267,12 +4326,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4292,7 +4351,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4312,7 +4371,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -4332,7 +4391,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -4352,7 +4411,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4367,12 +4426,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -4392,7 +4451,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -4412,7 +4471,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4432,7 +4491,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4452,7 +4511,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -4467,20 +4526,20 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -461,13 +461,13 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Última respuesta</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -517,12 +517,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>¿Ya está en SAPO?</t>
+          <t>¿Ya estaba en SAPO?</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Observación</t>
+          <t>Veces que respondió</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L2"/>
@@ -596,7 +598,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -636,7 +638,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Veces reportada</t>
+          <t>Vendedores que la reportaron</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -656,7 +658,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>¿Ya está en SAPO?</t>
+          <t>¿Ya estaba en SAPO?</t>
         </is>
       </c>
     </row>
@@ -704,17 +706,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -724,17 +726,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -744,17 +746,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -764,17 +766,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -784,17 +786,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -804,17 +806,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -824,17 +826,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -844,17 +846,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -864,17 +866,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -884,17 +886,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -904,17 +906,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -924,17 +926,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -944,17 +946,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CRECOS CUENCA</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -964,17 +966,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -984,17 +986,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1004,17 +1006,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL CARMEN</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1024,17 +1026,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1044,17 +1046,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1064,17 +1066,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL GUASMO</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1084,17 +1086,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1104,17 +1106,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1124,17 +1126,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1144,17 +1146,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1164,17 +1166,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1184,17 +1186,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1204,17 +1206,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1224,17 +1226,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1244,17 +1246,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1264,17 +1266,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1284,17 +1286,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1304,17 +1306,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1324,17 +1326,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1344,17 +1346,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1364,17 +1366,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1384,17 +1386,17 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1404,17 +1406,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>CRECOS MANTA</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1424,17 +1426,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>CRECOS MILAGRO</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1444,17 +1446,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1464,17 +1466,17 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1484,17 +1486,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1504,17 +1506,17 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>CRECOS OTAVALO</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1524,17 +1526,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1544,17 +1546,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>CRECOS PEDERNALES</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1564,17 +1566,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1584,17 +1586,17 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>CRECOS PINAS</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1604,17 +1606,17 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>CRECOS PLAYAS</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1624,17 +1626,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1644,17 +1646,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1664,17 +1666,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTETE</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1684,17 +1686,17 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1704,17 +1706,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1724,17 +1726,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>CRECOS QUEVEDO</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1744,17 +1746,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1764,17 +1766,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1784,17 +1786,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1804,17 +1806,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1824,17 +1826,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1844,17 +1846,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1864,17 +1866,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1884,17 +1886,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1904,17 +1906,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1924,17 +1926,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>CRECOS TUMBACO</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -1944,17 +1946,17 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>JAPON AMBATO</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -1964,17 +1966,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>JAPON BABAHOYO</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -1984,17 +1986,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>JAPON CALDERON</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2004,17 +2006,17 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>JAPON CARAPUNGO</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2024,17 +2026,17 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>JAPON CAYAMBE</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2044,17 +2046,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2064,17 +2066,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>JAPON CHONE</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2084,17 +2086,17 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2104,17 +2106,17 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2124,17 +2126,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>JAPON EL QUINCHE</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2144,17 +2146,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 1</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2164,17 +2166,17 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 2</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -2184,17 +2186,17 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>JAPON ESMERALDAS</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2204,17 +2206,17 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>JAPON GUAMANI</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2224,17 +2226,17 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>JAPON IBARRA 1</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2244,17 +2246,17 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>JAPON IBARRA 2</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2264,17 +2266,17 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2284,17 +2286,17 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2304,17 +2306,17 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2324,17 +2326,17 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>JAPON LA PRENSA</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2344,17 +2346,17 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>JAPON LATACUNGA</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -2364,17 +2366,17 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>JAPON LOJA</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -2384,17 +2386,17 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>JAPON MACHACHI</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -2404,17 +2406,17 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>JAPON MACHALA</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -2424,17 +2426,17 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2444,17 +2446,17 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -2464,17 +2466,17 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>JAPON MANTA 1</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2484,17 +2486,17 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>JAPON MANTA 2</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -2504,17 +2506,17 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>JAPON MILAGRO</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -2524,17 +2526,17 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2544,17 +2546,17 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -2564,17 +2566,17 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>JAPON PASAJE</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -2584,17 +2586,17 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -2604,17 +2606,17 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -2624,17 +2626,17 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>JAPON QUEVEDO</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -2644,17 +2646,17 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -2664,17 +2666,17 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>JAPON RIOBAMBA</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -2684,17 +2686,17 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -2704,17 +2706,17 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>JAPON SANGOLQUI</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -2724,17 +2726,17 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>JAPON SANTA ROSA</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -2744,17 +2746,17 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -2764,17 +2766,17 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -2784,17 +2786,17 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -2804,17 +2806,17 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>JAPON TUMBACO</t>
         </is>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -2824,17 +2826,17 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE AMBATO</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -2844,17 +2846,17 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -2864,17 +2866,17 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -2884,17 +2886,17 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE EL COCA</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -2904,17 +2906,17 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -2924,17 +2926,17 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -2944,17 +2946,17 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -2964,17 +2966,17 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -2984,17 +2986,17 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -3004,17 +3006,17 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -3024,17 +3026,17 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -3044,17 +3046,17 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -3064,17 +3066,17 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -3084,17 +3086,17 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -3104,17 +3106,17 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -3124,17 +3126,17 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE VINCES</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -3144,17 +3146,17 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Multinivel</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>MULTINIVEL (sin agencia)</t>
         </is>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -3164,17 +3166,17 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -3184,17 +3186,17 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>ORVE ALBORADA</t>
         </is>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -3204,17 +3206,17 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>ORVE AMBATO</t>
         </is>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -3224,17 +3226,17 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>ORVE BABAHOYO</t>
         </is>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -3244,17 +3246,17 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>ORVE BALZAR</t>
         </is>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -3264,17 +3266,17 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>ORVE CALCETA</t>
         </is>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -3284,17 +3286,17 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>ORVE CALDERON</t>
         </is>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -3304,17 +3306,17 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>ORVE CARAPUNGO</t>
         </is>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -3324,17 +3326,17 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>ORVE CAYAMBE</t>
         </is>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -3344,17 +3346,17 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>ORVE CHONE</t>
         </is>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -3364,17 +3366,17 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -3384,17 +3386,17 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>ORVE CUENCA 1</t>
         </is>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -3404,17 +3406,17 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>ORVE DAULE</t>
         </is>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -3424,17 +3426,17 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -3444,17 +3446,17 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>ORVE EL ARENAL</t>
         </is>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -3464,17 +3466,17 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>ORVE EL CARMEN</t>
         </is>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -3484,17 +3486,17 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>ORVE EL QUINCHE</t>
         </is>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -3504,17 +3506,17 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>ORVE EL RECREO 1</t>
         </is>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -3524,17 +3526,17 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>ORVE EL RECREO 2</t>
         </is>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -3544,17 +3546,17 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>ORVE EL RECREO 3</t>
         </is>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -3564,17 +3566,17 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>ORVE ESMERALDAS</t>
         </is>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -3584,17 +3586,17 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>ORVE GUAMANI</t>
         </is>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -3604,17 +3606,17 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>ORVE GUARANDA</t>
         </is>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -3624,17 +3626,17 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>ORVE IBARRA 1</t>
         </is>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -3644,17 +3646,17 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>ORVE JIPIJAPA</t>
         </is>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -3664,17 +3666,17 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -3684,17 +3686,17 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -3704,17 +3706,17 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>ORVE LA PRENSA</t>
         </is>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -3724,17 +3726,17 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -3744,17 +3746,17 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -3764,17 +3766,17 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>ORVE LOJA</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -3784,17 +3786,17 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>ORVE MACHACHI</t>
         </is>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -3804,17 +3806,17 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>ORVE MACHALA 2</t>
         </is>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -3824,17 +3826,17 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -3844,17 +3846,17 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>ORVE MANTA 1</t>
         </is>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -3864,17 +3866,17 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>ORVE MILAGRO</t>
         </is>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -3884,17 +3886,17 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C161" t="n">
+      <c r="C161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -3904,17 +3906,17 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>ORVE NARANJITO</t>
         </is>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -3924,17 +3926,17 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -3944,17 +3946,17 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>ORVE OTAVALO</t>
         </is>
       </c>
-      <c r="C164" t="n">
+      <c r="C164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -3964,17 +3966,17 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -3984,17 +3986,17 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>ORVE PEDERNALES</t>
         </is>
       </c>
-      <c r="C166" t="n">
+      <c r="C166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -4004,17 +4006,17 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>ORVE PIFO</t>
         </is>
       </c>
-      <c r="C167" t="n">
+      <c r="C167" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -4024,17 +4026,17 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>ORVE PINAS</t>
         </is>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -4044,17 +4046,17 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>ORVE PLAYAS</t>
         </is>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -4064,17 +4066,17 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>ORVE PORTETE</t>
         </is>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -4084,17 +4086,17 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -4104,17 +4106,17 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -4124,17 +4126,17 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>ORVE QUEVEDO</t>
         </is>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -4144,17 +4146,17 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -4164,17 +4166,17 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>ORVE QUININDE</t>
         </is>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -4184,17 +4186,17 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -4204,17 +4206,17 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>ORVE SANGOLQUI</t>
         </is>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -4224,17 +4226,17 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>ORVE SANTA ANA</t>
         </is>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -4244,17 +4246,17 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -4264,17 +4266,17 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -4284,17 +4286,17 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>ORVE TUMBACO</t>
         </is>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -4304,17 +4306,17 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>ORVE VINCES</t>
         </is>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -4324,17 +4326,17 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>PAGA MENOS CHONE</t>
         </is>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -4344,17 +4346,17 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>PAGA MENOS DAULE</t>
         </is>
       </c>
-      <c r="C184" t="n">
+      <c r="C184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -4364,17 +4366,17 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C185" t="n">
+      <c r="C185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -4384,17 +4386,17 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C186" t="n">
+      <c r="C186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -4404,17 +4406,17 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
-      <c r="C187" t="n">
+      <c r="C187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -4424,17 +4426,17 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
-      <c r="C188" t="n">
+      <c r="C188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -4444,17 +4446,17 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
-      <c r="C189" t="n">
+      <c r="C189" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -4464,17 +4466,17 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
-      <c r="C190" t="n">
+      <c r="C190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -4484,17 +4486,17 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C191" t="n">
+      <c r="C191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -4504,17 +4506,17 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
-      <c r="C192" t="n">
+      <c r="C192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D192" s="2" t="inlineStr">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +34,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -70,21 +63,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -447,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -526,59 +516,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:53</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>César Izquierdo</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>JAPON CUENCA</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>@cdizquierdoc</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-  </hyperlinks>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2133,7 +2072,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -2153,7 +2092,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -2173,7 +2112,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2193,7 +2132,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -2213,7 +2152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -2233,7 +2172,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -2253,7 +2192,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2273,7 +2212,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2293,7 +2232,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2313,7 +2252,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -2333,7 +2272,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -2353,7 +2292,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -2373,7 +2312,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -2393,7 +2332,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -2413,7 +2352,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -2433,7 +2372,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -2453,7 +2392,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -2473,7 +2412,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -2493,7 +2432,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -2513,7 +2452,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -2533,7 +2472,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -2553,7 +2492,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -2573,7 +2512,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -2593,7 +2532,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -2613,7 +2552,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -2633,7 +2572,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -2653,7 +2592,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -2673,7 +2612,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -2693,7 +2632,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -2713,7 +2652,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -2733,7 +2672,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -2753,7 +2692,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -2773,7 +2712,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -2793,7 +2732,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -2813,7 +2752,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -2828,12 +2767,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -2853,7 +2792,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -2873,7 +2812,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -2893,7 +2832,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -2913,7 +2852,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -2933,7 +2872,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -2953,7 +2892,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -2973,7 +2912,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -2993,7 +2932,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -3013,7 +2952,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -3033,7 +2972,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -3053,7 +2992,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -3073,7 +3012,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -3093,7 +3032,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -3113,7 +3052,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -3133,7 +3072,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -3148,12 +3087,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Multinivel</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>MULTINIVEL (sin agencia)</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -3168,12 +3107,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Multinivel</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>MULTINIVEL (sin agencia)</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -3193,7 +3132,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
@@ -3213,7 +3152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -3233,7 +3172,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -3253,7 +3192,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -3273,7 +3212,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -3293,7 +3232,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -3313,7 +3252,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -3333,7 +3272,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -3353,7 +3292,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -3373,7 +3312,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -3393,7 +3332,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -3413,7 +3352,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -3433,7 +3372,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -3453,7 +3392,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -3473,7 +3412,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -3493,7 +3432,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -3513,7 +3452,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -3533,7 +3472,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -3553,7 +3492,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
@@ -3573,7 +3512,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
@@ -3593,7 +3532,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
@@ -3613,7 +3552,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
@@ -3633,7 +3572,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
@@ -3653,7 +3592,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
@@ -3673,7 +3612,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
@@ -3693,7 +3632,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
@@ -3713,7 +3652,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
@@ -3733,7 +3672,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
@@ -3753,7 +3692,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
@@ -3773,7 +3712,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
@@ -3793,7 +3732,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
@@ -3813,7 +3752,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
@@ -3833,7 +3772,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
@@ -3853,7 +3792,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
@@ -3873,7 +3812,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
@@ -3893,7 +3832,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
@@ -3913,7 +3852,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
@@ -3933,7 +3872,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
@@ -3953,7 +3892,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
@@ -3973,7 +3912,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE OTAVALO</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
@@ -3993,7 +3932,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
@@ -4013,7 +3952,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
@@ -4033,7 +3972,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
@@ -4053,7 +3992,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
@@ -4073,7 +4012,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
@@ -4093,7 +4032,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
@@ -4113,7 +4052,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 3</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
@@ -4133,7 +4072,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
@@ -4153,7 +4092,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
@@ -4173,7 +4112,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
@@ -4193,7 +4132,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
@@ -4213,7 +4152,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
@@ -4233,7 +4172,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANGOLQUI</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
@@ -4253,7 +4192,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
@@ -4273,7 +4212,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
@@ -4293,7 +4232,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
@@ -4313,7 +4252,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
@@ -4328,12 +4267,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
@@ -4353,7 +4292,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
@@ -4373,7 +4312,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
@@ -4393,7 +4332,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
@@ -4413,7 +4352,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
@@ -4428,12 +4367,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
@@ -4453,7 +4392,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
@@ -4473,7 +4412,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
@@ -4493,7 +4432,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
@@ -4513,35 +4452,35 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Sin respuestas</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
           <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
-      <c r="C192" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>JAPON CUENCA</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>1</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="C193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Sin respuestas</t>
         </is>
       </c>
     </row>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -1887,12 +1887,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -2787,12 +2787,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -3107,12 +3107,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Multinivel</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>MULTINIVEL (sin agencia)</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,45 +529,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -580,10 +569,119 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>72</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L4"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1519,7 +1617,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS PEDERNALES</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -1539,7 +1637,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PEDERNALES</t>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -1559,7 +1657,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+          <t>CRECOS PINAS</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -1579,7 +1677,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PINAS</t>
+          <t>CRECOS PLAYAS</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -1599,7 +1697,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PLAYAS</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -1619,7 +1717,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -1639,7 +1737,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTAL SHOPPING</t>
+          <t>CRECOS PORTETE</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -1659,7 +1757,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTETE</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -1679,7 +1777,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -1699,7 +1797,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -1719,7 +1817,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -1739,7 +1837,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -1759,7 +1857,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -1779,7 +1877,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -1799,7 +1897,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -1819,7 +1917,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -1839,7 +1937,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -1859,7 +1957,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -1879,7 +1977,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -1899,7 +1997,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -1914,12 +2012,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -1934,12 +2032,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -1959,7 +2057,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -1979,7 +2077,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -1999,7 +2097,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -2019,7 +2117,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -2039,7 +2137,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -2059,7 +2157,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -2079,7 +2177,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -2099,7 +2197,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -2119,7 +2217,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -2139,7 +2237,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -2159,7 +2257,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -2179,7 +2277,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -2199,7 +2297,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -2219,7 +2317,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -2239,7 +2337,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -2259,7 +2357,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -2279,7 +2377,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -2299,7 +2397,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -2319,7 +2417,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -2339,7 +2437,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -2359,7 +2457,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -2379,7 +2477,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -2399,7 +2497,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -2419,7 +2517,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -2439,7 +2537,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -2459,7 +2557,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -2479,7 +2577,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -2499,7 +2597,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -2519,7 +2617,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -2539,7 +2637,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -2559,7 +2657,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -2579,7 +2677,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -2599,7 +2697,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -2619,7 +2717,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -2639,7 +2737,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -2659,7 +2757,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -2679,7 +2777,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -2699,7 +2797,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -2719,7 +2817,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -2739,7 +2837,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -2759,7 +2857,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -2779,7 +2877,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -2799,7 +2897,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -2819,7 +2917,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -2834,12 +2932,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -2859,7 +2957,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -2879,7 +2977,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -2899,7 +2997,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -2919,7 +3017,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -2939,7 +3037,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -2959,7 +3057,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -2979,7 +3077,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -2999,7 +3097,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -3019,7 +3117,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -3039,7 +3137,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -3059,7 +3157,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -3079,7 +3177,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -3099,7 +3197,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -3119,7 +3217,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -3139,7 +3237,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -3154,12 +3252,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -3179,7 +3277,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -3199,7 +3297,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -3219,7 +3317,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -3239,7 +3337,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -3259,7 +3357,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -3279,7 +3377,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -3299,7 +3397,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -3319,7 +3417,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -3339,7 +3437,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -3359,7 +3457,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -3379,7 +3477,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -3399,7 +3497,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -3419,7 +3517,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -3439,7 +3537,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -3459,7 +3557,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -3479,7 +3577,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -3499,7 +3597,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -3519,7 +3617,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -3539,7 +3637,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -3559,7 +3657,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -3579,7 +3677,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -3599,7 +3697,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -3619,7 +3717,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -3639,7 +3737,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -3659,7 +3757,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -3679,7 +3777,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -3699,7 +3797,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -3719,7 +3817,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -3739,7 +3837,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -3759,7 +3857,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -3779,7 +3877,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -3799,7 +3897,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -3819,7 +3917,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -3839,7 +3937,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -3859,7 +3957,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -3879,7 +3977,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -3899,7 +3997,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -3919,7 +4017,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -3939,7 +4037,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -3959,7 +4057,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -3979,7 +4077,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -3999,7 +4097,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -4019,7 +4117,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -4039,7 +4137,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -4059,7 +4157,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -4079,7 +4177,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -4099,7 +4197,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -4119,7 +4217,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 3</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -4139,7 +4237,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -4159,7 +4257,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -4179,7 +4277,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE SANGOLQUI</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -4199,7 +4297,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -4219,7 +4317,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -4239,7 +4337,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -4259,7 +4357,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -4279,7 +4377,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -4294,12 +4392,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -4314,12 +4412,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -4339,7 +4437,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -4359,7 +4457,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -4379,7 +4477,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -4394,12 +4492,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -4414,12 +4512,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
@@ -4439,7 +4537,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -4459,7 +4557,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -4479,7 +4577,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
@@ -4492,54 +4590,54 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>ORVE OTAVALO</t>
         </is>
       </c>
       <c r="C193" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,12 +529,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,19 +544,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -570,101 +581,84 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Aaron Reasco</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>72</v>
-      </c>
-      <c r="I3" t="inlineStr">
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -677,11 +671,224 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Miguel Coello</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>309</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>César Roberto Maldonado Carlozama</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>72</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L8"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1877,7 +2084,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -1897,7 +2104,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -1917,7 +2124,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -1937,7 +2144,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -1957,7 +2164,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -1977,7 +2184,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -1992,12 +2199,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -2012,12 +2219,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -2037,7 +2244,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -2057,7 +2264,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -2077,7 +2284,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -2097,7 +2304,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -2117,7 +2324,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -2137,7 +2344,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -2157,7 +2364,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -2177,7 +2384,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -2197,7 +2404,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -2217,7 +2424,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -2237,7 +2444,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -2257,7 +2464,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -2277,7 +2484,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -2297,7 +2504,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -2317,7 +2524,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -2337,7 +2544,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -2357,7 +2564,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -2377,7 +2584,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -2397,7 +2604,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -2417,7 +2624,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -2437,7 +2644,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -2457,7 +2664,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -2477,7 +2684,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -2497,7 +2704,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -2517,7 +2724,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -2537,7 +2744,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -2557,7 +2764,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -2577,7 +2784,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -2597,7 +2804,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -2617,7 +2824,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -2637,7 +2844,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -2657,7 +2864,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -2677,7 +2884,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -2697,7 +2904,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -2717,7 +2924,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -2737,7 +2944,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -2757,7 +2964,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -2777,7 +2984,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -2797,7 +3004,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -2817,7 +3024,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -2837,7 +3044,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -2857,7 +3064,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -2877,7 +3084,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -2897,7 +3104,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -2912,12 +3119,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -2937,7 +3144,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -2957,7 +3164,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -2977,7 +3184,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -2997,7 +3204,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -3017,7 +3224,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -3037,7 +3244,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -3057,7 +3264,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -3077,7 +3284,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -3097,7 +3304,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -3117,7 +3324,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -3137,7 +3344,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -3157,7 +3364,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -3177,7 +3384,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -3197,7 +3404,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -3212,12 +3419,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -3232,12 +3439,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -3257,7 +3464,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -3277,7 +3484,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -3297,7 +3504,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -3317,7 +3524,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -3337,7 +3544,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -3357,7 +3564,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -3377,7 +3584,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -3397,7 +3604,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -3417,7 +3624,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -3437,7 +3644,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -3457,7 +3664,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -3477,7 +3684,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -3497,7 +3704,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -3517,7 +3724,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -3537,7 +3744,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -3557,7 +3764,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -3577,7 +3784,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -3597,7 +3804,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -3617,7 +3824,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -3637,7 +3844,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -3657,7 +3864,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -3677,7 +3884,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -3697,7 +3904,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -3717,7 +3924,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -3737,7 +3944,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -3757,7 +3964,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -3777,7 +3984,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -3797,7 +4004,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -3817,7 +4024,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -3837,7 +4044,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -3857,7 +4064,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -3877,7 +4084,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -3897,7 +4104,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -3917,7 +4124,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -3937,7 +4144,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -3957,7 +4164,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -3977,7 +4184,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -3997,7 +4204,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -4017,7 +4224,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -4037,7 +4244,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -4057,7 +4264,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -4077,7 +4284,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -4097,7 +4304,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -4117,7 +4324,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -4137,7 +4344,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -4157,7 +4364,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -4177,7 +4384,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 3</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -4197,7 +4404,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -4217,7 +4424,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -4237,7 +4444,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -4257,7 +4464,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -4277,7 +4484,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -4297,7 +4504,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -4312,12 +4519,12 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -4332,12 +4539,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -4352,12 +4559,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -4372,12 +4579,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -4397,7 +4604,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -4412,12 +4619,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -4432,12 +4639,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -4452,12 +4659,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
@@ -4472,12 +4679,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
@@ -4497,7 +4704,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
@@ -4510,94 +4717,94 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4612,12 +4819,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>ORVE OTAVALO</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -4637,7 +4844,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE SANGOLQUI</t>
         </is>
       </c>
       <c r="C193" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,18 +559,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1698</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
@@ -588,7 +592,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Mykell Josué Zambrano Yagual</t>
+          <t>Jordano Zambrano</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -598,12 +602,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>@mykellteve</t>
+          <t>@jordanozambrano</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -631,12 +635,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -646,19 +650,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>dannyp109</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>280</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -674,12 +689,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,12 +704,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>@macclover23</t>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -704,22 +719,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>309</v>
+        <v>171</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -732,12 +743,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -747,19 +758,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -773,101 +795,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Aaron Reasco</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>72</v>
-      </c>
-      <c r="I7" t="inlineStr">
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -880,15 +885,229 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Miguel Coello</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>309</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>César Roberto Maldonado Carlozama</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>72</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1964,7 +2183,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -1984,7 +2203,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -2004,7 +2223,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -2024,7 +2243,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -2044,7 +2263,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -2064,7 +2283,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -2084,7 +2303,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -2104,7 +2323,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -2124,7 +2343,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -2144,7 +2363,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -2164,7 +2383,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -2179,12 +2398,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -2199,12 +2418,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -2224,7 +2443,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -2244,7 +2463,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -2264,7 +2483,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -2284,7 +2503,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -2304,7 +2523,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -2324,7 +2543,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -2344,7 +2563,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -2364,7 +2583,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -2384,7 +2603,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -2404,7 +2623,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -2424,7 +2643,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -2444,7 +2663,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -2464,7 +2683,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -2484,7 +2703,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -2504,7 +2723,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -2524,7 +2743,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -2544,7 +2763,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -2564,7 +2783,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -2584,7 +2803,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -2604,7 +2823,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -2624,7 +2843,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -2644,7 +2863,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -2664,7 +2883,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -2684,7 +2903,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -2704,7 +2923,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -2724,7 +2943,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -2744,7 +2963,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -2764,7 +2983,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -2784,7 +3003,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -2804,7 +3023,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -2824,7 +3043,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -2844,7 +3063,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -2864,7 +3083,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -2884,7 +3103,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -2904,7 +3123,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -2924,7 +3143,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -2944,7 +3163,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -2964,7 +3183,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -2984,7 +3203,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -3004,7 +3223,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -3024,7 +3243,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -3044,7 +3263,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -3064,7 +3283,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -3084,7 +3303,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -3099,12 +3318,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -3124,7 +3343,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -3144,7 +3363,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -3164,7 +3383,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -3184,7 +3403,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -3204,7 +3423,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -3224,7 +3443,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -3244,7 +3463,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -3264,7 +3483,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -3284,7 +3503,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -3304,7 +3523,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -3324,7 +3543,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -3344,7 +3563,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -3364,7 +3583,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -3379,12 +3598,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -3399,12 +3618,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -3424,7 +3643,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -3444,7 +3663,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -3464,7 +3683,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -3484,7 +3703,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -3504,7 +3723,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -3524,7 +3743,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -3544,7 +3763,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -3564,7 +3783,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -3584,7 +3803,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -3604,7 +3823,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -3624,7 +3843,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -3644,7 +3863,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -3664,7 +3883,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -3684,7 +3903,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -3704,7 +3923,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -3724,7 +3943,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -3744,7 +3963,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -3764,7 +3983,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -3784,7 +4003,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -3804,7 +4023,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -3824,7 +4043,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -3844,7 +4063,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -3864,7 +4083,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -3884,7 +4103,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -3904,7 +4123,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -3924,7 +4143,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -3944,7 +4163,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -3964,7 +4183,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -3984,7 +4203,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -4004,7 +4223,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -4024,7 +4243,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -4044,7 +4263,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -4064,7 +4283,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -4084,7 +4303,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -4104,7 +4323,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -4124,7 +4343,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -4144,7 +4363,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -4164,7 +4383,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -4184,7 +4403,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -4204,7 +4423,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -4224,7 +4443,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -4244,7 +4463,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -4264,7 +4483,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -4284,7 +4503,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -4304,7 +4523,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -4324,7 +4543,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 3</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -4344,7 +4563,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -4364,7 +4583,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -4384,7 +4603,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -4404,7 +4623,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -4424,7 +4643,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -4439,12 +4658,12 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -4459,12 +4678,12 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -4479,12 +4698,12 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -4499,12 +4718,12 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -4524,7 +4743,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -4539,12 +4758,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -4559,12 +4778,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -4579,12 +4798,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -4599,12 +4818,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
@@ -4624,7 +4843,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
@@ -4637,94 +4856,94 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4739,12 +4958,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -4759,12 +4978,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -4779,12 +4998,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4804,7 +5023,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C191" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -79,8 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -527,120 +527,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Christian Sánchez</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Edson Velez</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,33 +639,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>280</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -694,22 +672,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,18 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>171</v>
+        <v>1698</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -741,135 +723,146 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cristina Tenorio</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ORVE SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>@cristinaad67</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DANNY DAVID PINCAY PONCE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cristina AD</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>dannyp109</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>280</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>171</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>No</t>
@@ -888,27 +881,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -918,22 +911,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>Cristina AD</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -944,45 +933,50 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>César Roberto Maldonado Carlozama</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
+      <c r="L10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -994,40 +988,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1043,27 +1026,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,18 +1056,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>59</v>
+        <v>309</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1094,20 +1081,174 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>César Roberto Maldonado Carlozama</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>72</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:L15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1236,3622 +1377,3622 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL CARMEN</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL GUASMO</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>CRECOS MANTA</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>CRECOS MILAGRO</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>CRECOS OTAVALO</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>CRECOS PEDERNALES</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>CRECOS PINAS</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>CRECOS PLAYAS</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTETE</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>CRECOS QUEVEDO</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>CRECOS TUMBACO</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Independientes</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>JAPON AMBATO</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>JAPON AMBATO</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>JAPON BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>JAPON BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CALDERON</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CALDERON</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CHONE</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CHONE</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>JAPON COMITE DEL PUEBLO</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CUENCA</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CUENCA</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>JAPON ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>JAPON ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>JAPON GUAMANI</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>JAPON GUAMANI</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>JAPON IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>JAPON IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>JAPON IBARRA 2</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>JAPON IBARRA 2</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>JAPON ISLA MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LATACUNGA</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LATACUNGA</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LOJA</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LOJA</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MACHACHI</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MACHACHI</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MACHALA</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MACHALA</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MALL DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MALL DEL NORTE</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MALL DEL PACIFICO</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MALL DEL PACIFICO</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MANTA 1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MANTA 1</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MANTA 2</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MANTA 2</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MILAGRO</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MILAGRO</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>JAPON NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>JAPON NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PASAJE</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PASAJE</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 2</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 2</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>JAPON QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>JAPON QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>JAPON QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>JAPON QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>JAPON RIOBAMBA</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>JAPON RIOBAMBA</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SAN ANTONIO</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 1</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SCALA SHOPPING</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SCALA SHOPPING</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>JAPON TUMBACO</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>JAPON TUMBACO</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE AMBATO</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE AMBATO</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL COCA</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL COCA</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE VENTANAS</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE VENTANAS</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ORVE ALBORADA</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>ORVE ALBORADA</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ORVE AMBATO</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>ORVE AMBATO</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ORVE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>ORVE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ORVE BALZAR</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>ORVE BALZAR</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CALCETA</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CALCETA</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CALDERON</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CALDERON</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CHONE</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CHONE</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CUENCA 1</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>ORVE DAULE</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>ORVE DAULE</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL ARENAL</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL ARENAL</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 3</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>ORVE ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 3</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>ORVE GUAMANI</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>ORVE ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>ORVE GUARANDA</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>ORVE GUAMANI</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>ORVE IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>ORVE GUARANDA</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>ORVE IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LAGO AGRIO</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LATACUNGA 1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LAGO AGRIO</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LOJA</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LATACUNGA 1</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MACHACHI</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LOJA</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MACHALA 2</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MACHACHI</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MALL DEL SUR</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MACHALA 2</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MANTA 1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MALL DEL SUR</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MANTA 1</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NARANJITO</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NUEVA AURORA</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NARANJITO</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NUEVA AURORA</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PEDERNALES</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PIFO</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PEDERNALES</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PINAS</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PIFO</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTETE</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PINAS</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTETE</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUININDE</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>ORVE RIOBAMBA 1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTA ANA</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUININDE</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>ORVE RIOBAMBA 1</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTA ANA</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>ORVE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTA LUCIA</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>ORVE VINCES</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS CHONE</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>ORVE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS DAULE</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>ORVE VINCES</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS CHONE</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS DAULE</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG CITY MALL</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG EL DORADO</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG CITY MALL</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG QUICENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4863,7 +5004,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4878,12 +5019,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4898,12 +5039,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -4918,12 +5059,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -4938,12 +5079,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4958,12 +5099,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -4983,7 +5124,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -5003,7 +5144,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -5023,7 +5164,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE OTAVALO</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -5043,7 +5184,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="C192" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,8 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -527,54 +527,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Steeven</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Independientes</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>(sin agencia)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>@carlosasesordeorvehogar</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jofre Miguel Vélez Marcillo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@jofrevelez22</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Jofre Vélez</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>130</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -586,32 +588,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Edson Velez</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>724</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
@@ -624,37 +641,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Iván Quijije Cobeña</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>217</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -665,120 +693,114 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Christian Sánchez</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Mayra Arteaga Intriago</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>@mayra.arteaga212</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,27 +810,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>280</v>
-      </c>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>A veces</t>
@@ -827,48 +838,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EliYulexiAlcivar</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>171</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>@cristinaad67</t>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -911,18 +911,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1698</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -933,62 +937,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -998,19 +1002,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>dannyp109</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>280</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1026,12 +1041,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1041,12 +1056,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1056,22 +1071,18 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>309</v>
+        <v>171</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1084,12 +1095,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1099,19 +1110,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1125,101 +1147,84 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Aaron Reasco</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>72</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1232,23 +1237,237 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Miguel Coello</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>309</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>César Roberto Maldonado Carlozama</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>72</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L15"/>
+  <autoFilter ref="A1:L19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1260,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1333,8 +1552,64 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>@motopawer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marcimex</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Motopower</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1377,3562 +1652,3562 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL CARMEN</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL GUASMO</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>CRECOS MANTA</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>CRECOS MILAGRO</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CRECOS OTAVALO</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>CRECOS PEDERNALES</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CRECOS PINAS</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>CRECOS PLAYAS</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTETE</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>CRECOS QUEVEDO</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>CRECOS TUMBACO</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>JAPON AMBATO</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>JAPON BABAHOYO</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>JAPON CALDERON</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>JAPON CARAPUNGO</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>JAPON CAYAMBE</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>JAPON CHONE</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>JAPON CUENCA</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>JAPON EL QUINCHE</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 1</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 2</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>JAPON ESMERALDAS</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>JAPON GUAMANI</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>JAPON IBARRA 1</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>JAPON IBARRA 2</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>JAPON LA PRENSA</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>JAPON LATACUNGA</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>JAPON LOJA</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>JAPON MACHACHI</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>JAPON MACHALA</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>JAPON MANTA 1</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>JAPON MANTA 2</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>JAPON MILAGRO</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>JAPON PASAJE</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 2</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 2</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>JAPON QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>JAPON QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>JAPON QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>JAPON QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>JAPON RIOBAMBA</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>JAPON RIOBAMBA</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>JAPON SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>JAPON SAN ANTONIO</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>JAPON SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>JAPON SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>JAPON SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>JAPON SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 1</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 1</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>JAPON SCALA SHOPPING</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>JAPON SCALA SHOPPING</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>JAPON TUMBACO</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>JAPON TUMBACO</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE AMBATO</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE AMBATO</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL COCA</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL COCA</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE VENTANAS</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE VENTANAS</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>ORVE ALBORADA</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>ORVE ALBORADA</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>ORVE AMBATO</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>ORVE AMBATO</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>ORVE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>ORVE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>ORVE BALZAR</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>ORVE BALZAR</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CALCETA</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CALCETA</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CALDERON</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CALDERON</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CHONE</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CHONE</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>ORVE CUENCA 1</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>ORVE DAULE</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>ORVE DAULE</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>ORVE EL ARENAL</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>ORVE EL ARENAL</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 3</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 3</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>ORVE ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>ORVE ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>ORVE GUAMANI</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>ORVE GUAMANI</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>ORVE GUARANDA</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>ORVE GUARANDA</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>ORVE IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>ORVE IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LAGO AGRIO</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LAGO AGRIO</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LATACUNGA 1</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LATACUNGA 1</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LOJA</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LOJA</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MACHACHI</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MACHACHI</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MACHALA 2</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MACHALA 2</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MALL DEL SUR</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MALL DEL SUR</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MANTA 1</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MANTA 1</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>ORVE NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>ORVE NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>ORVE NARANJITO</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>ORVE NARANJITO</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>ORVE NUEVA AURORA</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>ORVE NUEVA AURORA</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PEDERNALES</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PEDERNALES</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PIFO</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PIFO</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PINAS</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PINAS</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTETE</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PORTETE</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>ORVE QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>ORVE QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>ORVE QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>ORVE QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>ORVE QUININDE</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>ORVE QUININDE</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>ORVE RIOBAMBA 1</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>ORVE RIOBAMBA 1</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>ORVE SANTA ANA</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>ORVE SANTA ANA</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>ORVE SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>ORVE SANTA LUCIA</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>ORVE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>ORVE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>ORVE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>ORVE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>ORVE VINCES</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>ORVE VINCES</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS CHONE</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS CHONE</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS DAULE</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS DAULE</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG CITY MALL</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG CITY MALL</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG EL DORADO</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG QUICENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5219,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4964,11 +5239,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4984,7 +5259,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4999,12 +5274,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -5019,12 +5294,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -5048,7 +5323,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,34 +529,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>karii🍒</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>178</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -577,32 +588,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1120</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
@@ -620,7 +646,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +668,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -658,12 +684,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -701,52 +727,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>231</v>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
@@ -757,62 +768,57 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Jesus andres</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>@creditorve</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Luis Medina Garcia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:23</t>
+          <t>2026-10-27 18:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ider Josue Rodriguez Sabando</t>
+          <t>Jhon Orellana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -822,24 +828,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>231</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>@crecoselcarmen</t>
+          <t>@crecos.duran</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -852,98 +869,81 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Jesus andres</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>130</v>
-      </c>
-      <c r="I9" t="inlineStr">
+          <t>@creditorve</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>724</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>A veces</t>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas88</t>
+          <t>@crecoselcarmen</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -966,27 +966,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -996,11 +996,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1018,200 +1018,226 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>724</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>217</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>@mayra.arteaga212</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L14" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Carlos Steeven</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Independientes</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>(sin agencia)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>@carlosasesordeorvehogar</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>@nouso</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:21</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1221,37 +1247,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1698</v>
-      </c>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>No</t>
@@ -1262,50 +1273,45 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Isaac Evaristo Wilson bohorquez</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1317,7 +1323,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1327,12 +1333,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>@dannyp109</t>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1342,18 +1348,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>dannyp109</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>280</v>
+        <v>1698</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1364,56 +1374,50 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL CARMEN</t>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>EliYulexiAlcivar</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>171</v>
-      </c>
-      <c r="I19" t="inlineStr">
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1435,12 +1439,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1450,15 +1454,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1472,62 +1476,68 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>171</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1537,19 +1547,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1563,60 +1584,50 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Miguel Coello</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>309</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1628,7 +1639,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1638,7 +1649,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1671,22 +1682,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>@aaronasesorce</t>
+          <t>@macclover23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1696,18 +1707,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>aaronasesorce</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>72</v>
+        <v>309</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>No</t>
@@ -1720,45 +1735,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1771,32 +1775,143 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>72</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>59</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L28"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2288,7 +2403,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS EL RECREO</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -2308,7 +2423,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CRECOS EL RECREO</t>
+          <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2328,7 +2443,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CRECOS ESMERALDAS</t>
+          <t>CRECOS GUARANDA</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -2348,7 +2463,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CRECOS GUARANDA</t>
+          <t>CRECOS IBARRA</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -2368,7 +2483,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CRECOS IBARRA</t>
+          <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -2388,7 +2503,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>CRECOS ISLA EL RECREO</t>
+          <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -2408,7 +2523,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>CRECOS JIPIJAPA</t>
+          <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -2428,7 +2543,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA CONCORDIA</t>
+          <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -2448,7 +2563,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA LIBERTAD</t>
+          <t>CRECOS LA PRENSA</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -2468,7 +2583,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA PRENSA</t>
+          <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -2488,7 +2603,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA TRONCAL</t>
+          <t>CRECOS LATACUNGA</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -2508,7 +2623,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LATACUNGA</t>
+          <t>CRECOS MACHALA</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -2528,7 +2643,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MACHALA</t>
+          <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -2548,7 +2663,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL NORTE</t>
+          <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -2568,7 +2683,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL PACIFICO</t>
+          <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -2588,7 +2703,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL SOL</t>
+          <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2608,7 +2723,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL SUR</t>
+          <t>CRECOS MANTA</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -2628,7 +2743,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MANTA</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2648,7 +2763,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2668,7 +2783,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NACIONES UNIDAS</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2688,7 +2803,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS NARANJITO</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2708,7 +2823,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJITO</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2728,7 +2843,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CRECOS OTAVALO</t>
+          <t>CRECOS PEDERNALES</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2748,7 +2863,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PEDERNALES</t>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2768,7 +2883,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+          <t>CRECOS PINAS</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2788,7 +2903,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PINAS</t>
+          <t>CRECOS PLAYAS</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2808,7 +2923,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PLAYAS</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2828,7 +2943,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2848,7 +2963,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTAL SHOPPING</t>
+          <t>CRECOS PORTETE</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2868,7 +2983,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTETE</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -2888,7 +3003,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -2908,7 +3023,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -2928,7 +3043,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -2948,7 +3063,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -2968,7 +3083,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -2988,7 +3103,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3008,7 +3123,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3028,7 +3143,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3048,7 +3163,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3068,7 +3183,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3083,12 +3198,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3108,7 +3223,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3128,7 +3243,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3148,7 +3263,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3168,7 +3283,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3188,7 +3303,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3208,7 +3323,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3228,7 +3343,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3248,7 +3363,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3268,7 +3383,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3288,7 +3403,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -3308,7 +3423,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -3328,7 +3443,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -3348,7 +3463,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -3368,7 +3483,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -3388,7 +3503,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -3408,7 +3523,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -3428,7 +3543,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -3448,7 +3563,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -3468,7 +3583,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -3488,7 +3603,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -3508,7 +3623,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -3528,7 +3643,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -3548,7 +3663,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -3568,7 +3683,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -3588,7 +3703,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -3608,7 +3723,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -3628,7 +3743,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -3648,7 +3763,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -3668,7 +3783,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -3688,7 +3803,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -3708,7 +3823,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -3728,7 +3843,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -3748,7 +3863,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -3768,7 +3883,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -3788,7 +3903,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -3808,7 +3923,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -3828,7 +3943,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -3848,7 +3963,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -3868,7 +3983,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -3888,7 +4003,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -3908,7 +4023,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -3928,7 +4043,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -3948,7 +4063,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -3963,12 +4078,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -3988,7 +4103,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -4008,7 +4123,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -4028,7 +4143,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -4048,7 +4163,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -4068,7 +4183,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -4088,7 +4203,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -4108,7 +4223,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -4128,7 +4243,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -4148,7 +4263,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -4168,7 +4283,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -4188,7 +4303,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -4203,12 +4318,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -4223,12 +4338,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -4248,7 +4363,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -4268,7 +4383,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -4288,7 +4403,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -4308,7 +4423,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -4328,7 +4443,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -4348,7 +4463,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -4368,7 +4483,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -4388,7 +4503,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -4408,7 +4523,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -4428,7 +4543,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -4448,7 +4563,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -4468,7 +4583,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -4488,7 +4603,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -4508,7 +4623,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -4528,7 +4643,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -4548,7 +4663,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -4568,7 +4683,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -4588,7 +4703,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -4608,7 +4723,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -4628,7 +4743,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -4648,7 +4763,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -4668,7 +4783,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -4688,7 +4803,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -4708,7 +4823,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -4728,7 +4843,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -4748,7 +4863,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -4768,7 +4883,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -4788,7 +4903,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -4808,7 +4923,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -4828,7 +4943,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -4848,7 +4963,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -4868,7 +4983,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -4888,7 +5003,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -4908,7 +5023,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -4928,7 +5043,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -4948,7 +5063,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -4968,7 +5083,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -4988,7 +5103,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -5008,7 +5123,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -5028,7 +5143,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -5048,7 +5163,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -5068,7 +5183,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -5088,7 +5203,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -5108,7 +5223,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -5128,7 +5243,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -5148,7 +5263,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -5168,7 +5283,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -5188,7 +5303,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -5203,12 +5318,12 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -5223,12 +5338,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -5248,7 +5363,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -5268,7 +5383,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -5288,7 +5403,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -5303,12 +5418,12 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -5323,12 +5438,12 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -5348,7 +5463,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -5368,7 +5483,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -5388,7 +5503,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -5401,42 +5516,42 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5563,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -5468,7 +5583,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -5488,7 +5603,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -5508,11 +5623,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -5528,11 +5643,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -5543,12 +5658,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -5563,12 +5678,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -5583,16 +5698,16 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -5608,11 +5723,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -5628,11 +5743,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5648,11 +5763,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,45 +529,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>178</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -583,27 +572,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>@vickman761</t>
+          <t>@karinamorn4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -613,22 +602,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>karii🍒</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1120</v>
+        <v>178</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
@@ -646,32 +631,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1120</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -689,17 +689,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -754,7 +754,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -770,22 +770,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -818,47 +818,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
@@ -869,97 +854,108 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>231</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Jesus andres</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>@creditorve</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -971,43 +967,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>130</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1020,27 +1009,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas1988</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1050,22 +1039,18 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1083,22 +1068,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@alvarovillegas1988</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1108,18 +1093,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>217</v>
+        <v>724</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1130,50 +1119,56 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Mayra Arteaga Intriago</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>@mayra.arteaga212</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr">
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>217</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1185,22 +1180,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Carlos Steeven</t>
+          <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>(sin agencia)</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>@carlosasesordeorvehogar</t>
+          <t>@mayra.arteaga212</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1212,14 +1207,10 @@
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1230,57 +1221,66 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>No</t>
@@ -1318,12 +1318,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1333,35 +1333,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>@orveduran</t>
+          <t>@isaacwilaon02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1374,104 +1359,108 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Christian Sánchez</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ORVE DURAN</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Jordano Zambrano</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>@jordanozambrano</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>280</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1483,22 +1472,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1508,15 +1497,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1537,22 +1526,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1562,15 +1551,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1584,93 +1573,104 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cristina Tenorio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Mykell Josué Zambrano Yagual</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>@mykellteve</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Luis Naranjo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1682,47 +1682,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>309</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>No</t>
@@ -1740,32 +1725,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>309</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>No</t>
@@ -1783,40 +1783,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1832,12 +1821,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Aaron Reasco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1847,12 +1836,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>@carlosalbertoterr85</t>
+          <t>@aaronasesorce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1862,15 +1851,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>aaronasesorce</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1883,35 +1872,89 @@
         <v>1</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>59</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L29"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2743,7 +2786,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -2763,7 +2806,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NACIONES UNIDAS</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2783,7 +2826,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS NARANJITO</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2803,7 +2846,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJITO</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2823,7 +2866,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CRECOS OTAVALO</t>
+          <t>CRECOS PEDERNALES</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2843,7 +2886,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PEDERNALES</t>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2863,7 +2906,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+          <t>CRECOS PINAS</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2883,7 +2926,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PINAS</t>
+          <t>CRECOS PLAYAS</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2903,7 +2946,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PLAYAS</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2923,7 +2966,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2943,7 +2986,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTAL SHOPPING</t>
+          <t>CRECOS PORTETE</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -2963,7 +3006,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTETE</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -2983,7 +3026,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -3003,7 +3046,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -3023,7 +3066,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3043,7 +3086,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3063,7 +3106,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3083,7 +3126,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3103,7 +3146,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3123,7 +3166,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3143,7 +3186,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3163,7 +3206,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3178,12 +3221,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3203,7 +3246,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3223,7 +3266,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3243,7 +3286,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3263,7 +3306,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3283,7 +3326,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3303,7 +3346,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3323,7 +3366,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3343,7 +3386,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3363,7 +3406,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3383,7 +3426,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3403,7 +3446,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -3423,7 +3466,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -3443,7 +3486,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -3463,7 +3506,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -3483,7 +3526,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -3503,7 +3546,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -3523,7 +3566,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -3543,7 +3586,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -3563,7 +3606,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -3583,7 +3626,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -3603,7 +3646,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -3623,7 +3666,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -3643,7 +3686,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -3663,7 +3706,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -3683,7 +3726,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -3703,7 +3746,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -3723,7 +3766,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -3743,7 +3786,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -3763,7 +3806,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -3783,7 +3826,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -3803,7 +3846,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -3823,7 +3866,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -3843,7 +3886,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -3863,7 +3906,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -3883,7 +3926,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -3903,7 +3946,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -3923,7 +3966,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -3943,7 +3986,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -3963,7 +4006,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -3983,7 +4026,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -4003,7 +4046,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -4023,7 +4066,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -4043,7 +4086,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -4058,12 +4101,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -4083,7 +4126,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -4103,7 +4146,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -4123,7 +4166,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -4143,7 +4186,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -4163,7 +4206,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -4183,7 +4226,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -4203,7 +4246,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -4223,7 +4266,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -4243,7 +4286,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -4263,7 +4306,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -4283,7 +4326,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -4298,12 +4341,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -4323,7 +4366,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -4343,7 +4386,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -4363,7 +4406,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -4383,7 +4426,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -4403,7 +4446,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -4423,7 +4466,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -4443,7 +4486,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -4463,7 +4506,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -4483,7 +4526,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -4503,7 +4546,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -4523,7 +4566,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -4543,7 +4586,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -4563,7 +4606,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -4583,7 +4626,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -4603,7 +4646,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -4623,7 +4666,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -4643,7 +4686,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -4663,7 +4706,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -4683,7 +4726,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -4703,7 +4746,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -4723,7 +4766,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -4743,7 +4786,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -4763,7 +4806,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -4783,7 +4826,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -4803,7 +4846,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -4823,7 +4866,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -4843,7 +4886,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -4863,7 +4906,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -4883,7 +4926,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -4903,7 +4946,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -4923,7 +4966,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -4943,7 +4986,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -4963,7 +5006,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -4983,7 +5026,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -5003,7 +5046,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -5023,7 +5066,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -5043,7 +5086,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -5063,7 +5106,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -5083,7 +5126,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -5103,7 +5146,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -5123,7 +5166,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -5143,7 +5186,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -5163,7 +5206,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -5183,7 +5226,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -5203,7 +5246,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -5223,7 +5266,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -5243,7 +5286,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -5263,7 +5306,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -5283,7 +5326,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -5298,12 +5341,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -5323,7 +5366,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -5343,7 +5386,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -5363,7 +5406,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -5383,7 +5426,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -5398,12 +5441,12 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -5423,7 +5466,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -5443,7 +5486,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -5463,7 +5506,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -5483,7 +5526,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -5496,22 +5539,22 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5566,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -5543,7 +5586,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -5563,7 +5606,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -5583,7 +5626,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C176" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,12 +529,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,19 +544,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Arleth Cali</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>182</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -572,45 +583,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>178</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -626,27 +626,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>@vickman761</t>
+          <t>@karinamorn4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -656,22 +656,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>karii🍒</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1120</v>
+        <v>178</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -689,32 +685,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1120</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -732,17 +743,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -775,17 +786,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -797,7 +808,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -813,22 +824,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -840,7 +851,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -861,47 +872,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -912,97 +908,108 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>231</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Jesus andres</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>@creditorve</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1014,43 +1021,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>130</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1063,27 +1063,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas1988</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1093,22 +1093,18 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1126,22 +1122,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@alvarovillegas1988</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1151,18 +1147,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>217</v>
+        <v>724</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1173,50 +1173,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Mayra Arteaga Intriago</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>@mayra.arteaga212</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr">
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>217</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1228,22 +1234,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Carlos Steeven</t>
+          <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>(sin agencia)</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>@carlosasesordeorvehogar</t>
+          <t>@mayra.arteaga212</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1255,14 +1261,10 @@
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1273,57 +1275,66 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1333,7 +1344,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1343,12 +1354,12 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1361,12 +1372,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1376,35 +1387,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>@orveduran</t>
+          <t>@isaacwilaon02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1417,104 +1413,108 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Christian Sánchez</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ORVE DURAN</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Jordano Zambrano</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>@jordanozambrano</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>280</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1526,22 +1526,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1551,15 +1551,15 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1580,22 +1580,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1605,15 +1605,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1627,93 +1627,104 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cristina Tenorio</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Mykell Josué Zambrano Yagual</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>@mykellteve</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Luis Naranjo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1725,47 +1736,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>309</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>No</t>
@@ -1783,32 +1779,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>309</v>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>No</t>
@@ -1826,40 +1837,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1875,12 +1875,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Aaron Reasco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>@carlosalbertoterr85</t>
+          <t>@aaronasesorce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1905,15 +1905,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>aaronasesorce</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1926,35 +1926,90 @@
         <v>1</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>59</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:L30"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2806,7 +2861,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS NARANJITO</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -2826,7 +2881,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJITO</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2846,7 +2901,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CRECOS OTAVALO</t>
+          <t>CRECOS PEDERNALES</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -2866,7 +2921,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PEDERNALES</t>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -2886,7 +2941,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+          <t>CRECOS PINAS</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -2906,7 +2961,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PINAS</t>
+          <t>CRECOS PLAYAS</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -2926,7 +2981,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PLAYAS</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -2946,7 +3001,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -2966,7 +3021,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTAL SHOPPING</t>
+          <t>CRECOS PORTETE</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -2986,7 +3041,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTETE</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -3006,7 +3061,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -3026,7 +3081,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -3046,7 +3101,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -3066,7 +3121,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3086,7 +3141,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3106,7 +3161,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3126,7 +3181,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3146,7 +3201,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3166,7 +3221,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3186,7 +3241,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3201,12 +3256,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3226,7 +3281,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3246,7 +3301,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3266,7 +3321,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3286,7 +3341,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3306,7 +3361,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3326,7 +3381,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3346,7 +3401,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3366,7 +3421,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3386,7 +3441,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3406,7 +3461,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3426,7 +3481,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3446,7 +3501,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -3466,7 +3521,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -3486,7 +3541,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -3506,7 +3561,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -3526,7 +3581,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -3546,7 +3601,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -3566,7 +3621,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -3586,7 +3641,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -3606,7 +3661,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -3626,7 +3681,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -3646,7 +3701,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -3666,7 +3721,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -3686,7 +3741,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -3706,7 +3761,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -3726,7 +3781,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -3746,7 +3801,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -3766,7 +3821,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -3786,7 +3841,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -3806,7 +3861,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -3826,7 +3881,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -3846,7 +3901,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -3866,7 +3921,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -3886,7 +3941,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -3906,7 +3961,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -3926,7 +3981,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -3946,7 +4001,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -3966,7 +4021,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -3986,7 +4041,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -4006,7 +4061,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -4026,7 +4081,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -4046,7 +4101,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -4066,7 +4121,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -4081,12 +4136,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -4106,7 +4161,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -4126,7 +4181,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -4146,7 +4201,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -4166,7 +4221,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -4186,7 +4241,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -4206,7 +4261,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -4226,7 +4281,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -4246,7 +4301,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -4266,7 +4321,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -4286,7 +4341,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -4306,7 +4361,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -4321,12 +4376,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -4346,7 +4401,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -4366,7 +4421,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -4386,7 +4441,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -4406,7 +4461,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -4426,7 +4481,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -4446,7 +4501,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -4466,7 +4521,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -4486,7 +4541,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -4506,7 +4561,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -4526,7 +4581,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -4546,7 +4601,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -4566,7 +4621,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -4586,7 +4641,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -4606,7 +4661,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -4626,7 +4681,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -4646,7 +4701,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -4666,7 +4721,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -4686,7 +4741,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -4706,7 +4761,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -4726,7 +4781,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -4746,7 +4801,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -4766,7 +4821,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -4786,7 +4841,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -4806,7 +4861,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -4826,7 +4881,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -4846,7 +4901,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -4866,7 +4921,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -4886,7 +4941,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -4906,7 +4961,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -4926,7 +4981,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -4946,7 +5001,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -4966,7 +5021,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -4986,7 +5041,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -5006,7 +5061,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -5026,7 +5081,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -5046,7 +5101,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -5066,7 +5121,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -5086,7 +5141,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -5106,7 +5161,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -5126,7 +5181,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -5146,7 +5201,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -5166,7 +5221,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -5186,7 +5241,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -5206,7 +5261,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -5226,7 +5281,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -5246,7 +5301,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -5266,7 +5321,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -5286,7 +5341,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -5306,7 +5361,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -5321,12 +5376,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -5346,7 +5401,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -5366,7 +5421,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -5386,7 +5441,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -5406,7 +5461,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -5421,12 +5476,12 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
@@ -5446,7 +5501,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -5466,7 +5521,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
@@ -5486,7 +5541,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
@@ -5506,7 +5561,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -5519,22 +5574,22 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5601,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5566,7 +5621,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -5586,7 +5641,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -5606,7 +5661,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -5626,7 +5681,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C176" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,12 +529,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:28</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arleth Cali</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,30 +547,19 @@
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>182</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
@@ -583,12 +572,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,19 +587,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arleth Cali</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>182</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -626,45 +626,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>178</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -680,27 +669,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>@vickman761</t>
+          <t>@karinamorn4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -710,22 +699,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>karii🍒</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1120</v>
+        <v>178</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -743,32 +728,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1120</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
@@ -786,17 +786,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -851,7 +851,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -867,22 +867,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -915,47 +915,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
@@ -966,97 +951,108 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>231</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Jesus andres</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>@creditorve</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1068,43 +1064,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>130</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1117,27 +1106,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas1988</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1147,22 +1136,18 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1180,22 +1165,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@alvarovillegas1988</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1205,18 +1190,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>217</v>
+        <v>724</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
@@ -1227,50 +1216,56 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Mayra Arteaga Intriago</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>@mayra.arteaga212</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr">
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>217</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1282,22 +1277,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Carlos Steeven</t>
+          <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>(sin agencia)</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>@carlosasesordeorvehogar</t>
+          <t>@mayra.arteaga212</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1309,14 +1304,10 @@
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1327,57 +1318,66 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>No</t>
@@ -1415,12 +1415,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1430,35 +1430,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>@orveduran</t>
+          <t>@isaacwilaon02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1471,104 +1456,108 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Christian Sánchez</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ORVE DURAN</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Jordano Zambrano</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>@jordanozambrano</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>280</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1580,22 +1569,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1605,15 +1594,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1634,22 +1623,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1659,15 +1648,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1681,93 +1670,104 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cristina Tenorio</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Mykell Josué Zambrano Yagual</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>@mykellteve</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Luis Naranjo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1779,47 +1779,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>309</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>No</t>
@@ -1837,32 +1822,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>309</v>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>No</t>
@@ -1880,40 +1880,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1929,12 +1918,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Aaron Reasco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1944,12 +1933,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>@carlosalbertoterr85</t>
+          <t>@aaronasesorce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1959,15 +1948,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>aaronasesorce</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1980,36 +1969,91 @@
         <v>1</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>59</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L30"/>
+  <autoFilter ref="A1:L31"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5685,7 +5729,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -79,8 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,22 +529,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:30</t>
+          <t>2026-10-27 18:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brian campos</t>
+          <t>Digno Gilses</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
@@ -570,68 +570,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:28</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>182</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:31</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Herrera Llamuca Jenny</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>@jennyherrera20</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -641,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -651,12 +645,12 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -669,27 +663,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -699,15 +693,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>karii🍒</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -723,12 +717,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -738,37 +732,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Victor Yanzapanta</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1120</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
@@ -781,34 +760,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>karii🍒</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>178</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -829,32 +819,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1120</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
@@ -872,7 +877,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -894,7 +899,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -910,12 +915,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -953,52 +958,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>231</v>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1009,62 +999,57 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Jesus andres</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>@creditorve</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Luis Medina Garcia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 18:23</t>
+          <t>2026-10-27 18:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ider Josue Rodriguez Sabando</t>
+          <t>Jhon Orellana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1074,24 +1059,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>231</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1104,106 +1100,89 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>130</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Jesus andres</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>@creditorve</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>724</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1218,27 +1197,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>@ivanquijije09</t>
+          <t>JAPON PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1248,11 +1227,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1270,200 +1249,226 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>724</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>217</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>@mayra.arteaga212</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Carlos Steeven</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Independientes</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>(sin agencia)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>@carlosasesordeorvehogar</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>@nouso</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:21</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
+      <c r="L20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1473,37 +1478,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1698</v>
-      </c>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>No</t>
@@ -1514,50 +1504,45 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Isaac Evaristo Wilson bohorquez</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1569,7 +1554,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1579,12 +1564,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1594,18 +1579,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>dannyp109</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>280</v>
+        <v>1698</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>No</t>
@@ -1616,56 +1605,50 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>EliYulexiAlcivar</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>171</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1677,7 +1660,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1687,12 +1670,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>@cristinaad67</t>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1702,15 +1685,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1724,62 +1707,68 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>171</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1789,19 +1778,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1815,60 +1815,50 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Miguel Coello</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>309</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1880,7 +1870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1890,7 +1880,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1923,22 +1913,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1948,18 +1938,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>aaronasesorce</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>72</v>
+        <v>309</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>No</t>
@@ -1972,45 +1966,34 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2023,37 +2006,146 @@
         <v>1</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>72</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>59</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:L33"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2139,7 +2231,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>@motopawer</t>
         </is>
@@ -2238,3382 +2330,3382 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>CRECOS MANTA</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>CRECOS OTAVALO</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>CRECOS PEDERNALES</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>CRECOS PINAS</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>CRECOS PLAYAS</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTAL SHOPPING</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTAL SHOPPING</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTETE</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTETE</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 2</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 2</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS RIOCENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS RIOCENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS RIOCENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SAN VICENTE</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANTO DOMINGO 1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS TUMBACO</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS TUMBACO</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>JAPON AMBATO</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JAPON AMBATO</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>JAPON BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>JAPON BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CALDERON</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CALDERON</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CHONE</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CHONE</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>JAPON COMITE DEL PUEBLO</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CUENCA</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CUENCA</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>JAPON ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>JAPON ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>JAPON GUAMANI</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>JAPON GUAMANI</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>JAPON IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>JAPON IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>JAPON IBARRA 2</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>JAPON IBARRA 2</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>JAPON ISLA MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LATACUNGA</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LATACUNGA</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LOJA</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LOJA</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MACHACHI</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MACHACHI</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MACHALA</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MACHALA</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MALL DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MALL DEL NORTE</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MALL DEL PACIFICO</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MALL DEL PACIFICO</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MANTA 1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MANTA 1</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MANTA 2</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MANTA 2</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MILAGRO</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MILAGRO</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>JAPON NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>JAPON NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PASAJE</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PASAJE</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 2</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 2</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>JAPON QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>JAPON QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>JAPON QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>JAPON QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>JAPON RIOBAMBA</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>JAPON RIOBAMBA</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SAN ANTONIO</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 1</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SCALA SHOPPING</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SCALA SHOPPING</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>JAPON TUMBACO</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>JAPON TUMBACO</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE AMBATO</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE AMBATO</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL COCA</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL COCA</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE VENTANAS</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE VENTANAS</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ORVE ALBORADA</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>ORVE ALBORADA</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ORVE AMBATO</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>ORVE AMBATO</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ORVE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>ORVE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ORVE BALZAR</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>ORVE BALZAR</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CALCETA</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CALCETA</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CALDERON</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CALDERON</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CHONE</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CHONE</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CUENCA 1</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ORVE DAULE</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>ORVE DAULE</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL ARENAL</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL ARENAL</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 3</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>ORVE ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 3</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ORVE GUAMANI</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>ORVE ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>ORVE GUARANDA</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>ORVE GUAMANI</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ORVE IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>ORVE GUARANDA</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>ORVE IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LAGO AGRIO</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LATACUNGA 1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LAGO AGRIO</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LOJA</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LATACUNGA 1</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MACHACHI</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LOJA</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MACHALA 2</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MACHACHI</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MALL DEL SUR</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MACHALA 2</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MANTA 1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MALL DEL SUR</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MANTA 1</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NARANJITO</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NUEVA AURORA</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NARANJITO</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NUEVA AURORA</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PEDERNALES</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PIFO</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PEDERNALES</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PINAS</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PIFO</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTETE</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PINAS</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTETE</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUININDE</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>ORVE RIOBAMBA 1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUININDE</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTA ANA</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>ORVE RIOBAMBA 1</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTA ANA</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTA LUCIA</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>ORVE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>ORVE VINCES</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>ORVE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS CHONE</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>ORVE VINCES</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS DAULE</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS CHONE</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS DAULE</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG CITY MALL</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG CITY MALL</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG EL DORADO</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG QUICENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5717,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -5645,7 +5737,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5665,7 +5757,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -5685,11 +5777,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -5705,7 +5797,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -5725,11 +5817,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -5745,11 +5837,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -5765,11 +5857,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -5780,12 +5872,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -5800,12 +5892,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -5820,16 +5912,16 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -5845,11 +5937,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -5865,11 +5957,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -5885,11 +5977,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5900,12 +5992,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -5925,7 +6017,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -5945,7 +6037,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -5965,7 +6057,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -5985,7 +6077,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C189" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -534,17 +534,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Digno Gilses</t>
+          <t>Carlos Vargas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -570,105 +570,105 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:32</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Digno Gilses</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:31</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Herrera Llamuca Jenny</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>@jennyherrera20</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:30</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brian campos</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:28</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arleth Cali</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -681,30 +681,19 @@
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>182</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -717,12 +706,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -732,19 +721,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Arleth Cali</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>182</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -760,45 +760,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>178</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -814,27 +803,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>@vickman761</t>
+          <t>@karinamorn4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -844,22 +833,18 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>karii🍒</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1120</v>
+        <v>178</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
@@ -877,32 +862,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1120</v>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -920,17 +920,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -963,17 +963,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -985,7 +985,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1001,22 +1001,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1049,47 +1049,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1100,97 +1085,108 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>231</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Jesus andres</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>@creditorve</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
+      <c r="L15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1202,43 +1198,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>130</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>No</t>
@@ -1251,27 +1240,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>@alvarovillegas1988</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1281,22 +1270,18 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>No</t>
@@ -1314,22 +1299,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@alvarovillegas1988</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1339,18 +1324,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>217</v>
+        <v>724</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1361,50 +1350,56 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Mayra Arteaga Intriago</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>@mayra.arteaga212</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>217</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1416,22 +1411,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Carlos Steeven</t>
+          <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>(sin agencia)</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>@carlosasesordeorvehogar</t>
+          <t>@mayra.arteaga212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1443,14 +1438,10 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1461,57 +1452,66 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>No</t>
@@ -1549,12 +1549,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1564,35 +1564,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>@orveduran</t>
+          <t>@isaacwilaon02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1605,104 +1590,108 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Christian Sánchez</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ORVE DURAN</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Jordano Zambrano</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>@jordanozambrano</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>280</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="L25" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1714,22 +1703,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1739,15 +1728,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1768,22 +1757,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1793,15 +1782,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1815,93 +1804,104 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cristina Tenorio</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Mykell Josué Zambrano Yagual</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>@mykellteve</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Luis Naranjo</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
+      <c r="L29" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1913,47 +1913,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>309</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>No</t>
@@ -1971,32 +1956,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>309</v>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>No</t>
@@ -2014,40 +2014,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -2063,12 +2052,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Aaron Reasco</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2078,12 +2067,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>@carlosalbertoterr85</t>
+          <t>@aaronasesorce</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2093,15 +2082,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>aaronasesorce</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -2114,38 +2103,92 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>59</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
+  <autoFilter ref="A1:L34"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5821,7 +5864,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -79,8 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,37 +529,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>JEAMPIERRE MORAN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@orvejipijapa</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>OrveHogar Jipijapa</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1016</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>@sn</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
@@ -577,17 +592,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Digno Gilses</t>
+          <t>Carlos Vargas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -613,105 +628,105 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:32</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Digno Gilses</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:31</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Herrera Llamuca Jenny</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>@jennyherrera20</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brian campos</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:28</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arleth Cali</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -724,30 +739,19 @@
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>182</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
@@ -760,12 +764,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -775,19 +779,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Arleth Cali</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>182</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -803,45 +818,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>178</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -857,27 +861,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -887,22 +891,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>karii🍒</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1120</v>
+        <v>178</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -920,32 +920,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1120</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
@@ -963,17 +978,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,17 +1021,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1028,7 +1043,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1044,22 +1059,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1071,7 +1086,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1092,47 +1107,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1143,97 +1143,108 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>231</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Jesus andres</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>@creditorve</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1245,43 +1256,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>130</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>No</t>
@@ -1294,27 +1298,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
+          <t>JAPON PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1324,22 +1328,18 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1357,22 +1357,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>@ivanquijije09</t>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1382,18 +1382,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>217</v>
+        <v>724</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>No</t>
@@ -1404,157 +1408,168 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>217</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>@mayra.arteaga212</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L21" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Carlos Steeven</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Independientes</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>(sin agencia)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>@carlosasesordeorvehogar</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>@nouso</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1564,7 +1579,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1574,12 +1589,12 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>No</t>
@@ -1592,12 +1607,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1607,35 +1622,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1648,104 +1648,108 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Christian Sánchez</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ORVE DURAN</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Jordano Zambrano</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>@jordanozambrano</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>280</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1757,22 +1761,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1782,15 +1786,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1811,22 +1815,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>@cristinaad67</t>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1836,15 +1840,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1858,93 +1862,104 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cristina Tenorio</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Mykell Josué Zambrano Yagual</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>@mykellteve</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L29" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Luis Naranjo</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1956,47 +1971,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>309</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>No</t>
@@ -2014,32 +2014,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>309</v>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>No</t>
@@ -2057,40 +2072,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -2106,12 +2110,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Aaron Reasco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2121,12 +2125,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2136,15 +2140,15 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>aaronasesorce</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -2157,38 +2161,94 @@
         <v>1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>59</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L35"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2274,7 +2334,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>@motopawer</t>
         </is>
@@ -2373,3342 +2433,3342 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>CRECOS MANTA</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>CRECOS OTAVALO</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>CRECOS PEDERNALES</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>CRECOS PINAS</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>CRECOS PLAYAS</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTETE</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CRECOS QUEVEDO</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CRECOS TUMBACO</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>JAPON AMBATO</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>JAPON BABAHOYO</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>JAPON CALDERON</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>JAPON CARAPUNGO</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>JAPON CAYAMBE</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>JAPON CHONE</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>JAPON CUENCA</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>JAPON EL QUINCHE</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 1</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 2</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>JAPON ESMERALDAS</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>JAPON GUAMANI</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>JAPON IBARRA 1</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>JAPON IBARRA 2</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>JAPON LA PRENSA</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>JAPON LATACUNGA</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>JAPON LOJA</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>JAPON MACHACHI</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>JAPON MACHALA</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>JAPON MANTA 1</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>JAPON MANTA 2</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>JAPON MILAGRO</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>JAPON PASAJE</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>JAPON QUEVEDO</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>JAPON RIOBAMBA</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>JAPON SANGOLQUI</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>JAPON SANTA ROSA</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>JAPON TUMBACO</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE AMBATO</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE EL COCA</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>ORVE ALBORADA</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>ORVE AMBATO</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>ORVE BABAHOYO</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>ORVE BALZAR</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>ORVE CALCETA</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>ORVE CALDERON</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>ORVE CARAPUNGO</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>ORVE CAYAMBE</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>ORVE CHONE</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>ORVE CUENCA 1</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>ORVE DAULE</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>ORVE EL ARENAL</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>ORVE EL RECREO 2</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>ORVE EL RECREO 3</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>ORVE ESMERALDAS</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>ORVE GUAMANI</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>ORVE GUARANDA</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>ORVE IBARRA 1</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LAGO AGRIO</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LAGO AGRIO</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LATACUNGA 1</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LATACUNGA 1</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>ORVE LOJA</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>ORVE LOJA</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MACHACHI</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MACHACHI</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MACHALA 2</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MACHALA 2</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MALL DEL SUR</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MALL DEL SUR</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MANTA 1</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MANTA 1</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>ORVE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>ORVE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>ORVE NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>ORVE NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>ORVE NARANJITO</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>ORVE NARANJITO</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>ORVE NUEVA AURORA</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>ORVE NUEVA AURORA</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PEDERNALES</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PEDERNALES</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PIFO</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PIFO</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PINAS</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PINAS</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTETE</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PORTETE</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>ORVE QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>ORVE QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>ORVE QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>ORVE QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>ORVE QUININDE</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>ORVE QUININDE</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>ORVE RIOBAMBA 1</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>ORVE RIOBAMBA 1</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>ORVE SANTA ANA</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>ORVE SANTA ANA</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>ORVE SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>ORVE SANTA LUCIA</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>ORVE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>ORVE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>ORVE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>ORVE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>ORVE VINCES</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>ORVE VINCES</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS CHONE</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS CHONE</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS DAULE</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS DAULE</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG CITY MALL</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG CITY MALL</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG EL DORADO</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>SAMSUNG QUICENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5780,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -5740,7 +5800,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -5760,7 +5820,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -5780,7 +5840,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5800,11 +5860,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -5820,11 +5880,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -5840,11 +5900,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -5860,11 +5920,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -5880,11 +5940,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -5895,12 +5955,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -5915,12 +5975,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -5935,16 +5995,16 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -5960,11 +6020,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -5980,11 +6040,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6000,11 +6060,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6015,12 +6075,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -6040,7 +6100,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -6060,7 +6120,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -6080,7 +6140,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -6100,7 +6160,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -6120,7 +6180,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>ORVE JIPIJAPA</t>
         </is>
       </c>
       <c r="C189" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JEAMPIERRE MORAN</t>
+          <t>Luis plata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,37 +544,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>@orvejipijapa</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>OrveHogar Jipijapa</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1016</v>
-      </c>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>@sn</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
@@ -587,34 +572,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>Boris Nicolay Toscano</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>@japon.chillogallo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>84</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -630,12 +626,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digno Gilses</t>
+          <t>JEAMPIERRE MORAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -645,22 +641,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>@orvejipijapa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OrveHogar Jipijapa</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1016</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>@sn</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -671,72 +682,67 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:31</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Herrera Llamuca Jenny</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>@jennyherrera20</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:30</t>
+          <t>2026-10-27 18:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brian campos</t>
+          <t>Digno Gilses</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,12 +752,12 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
@@ -762,68 +768,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:28</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Herrera Llamuca Jenny</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>182</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+          <t>@jennyherrera20</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
@@ -861,27 +861,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>@karinamorn4</t>
+          <t>@arlethcali</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -891,15 +891,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>karii🍒</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -915,12 +915,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -930,37 +930,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Victor Yanzapanta</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1120</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
@@ -973,34 +958,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>karii🍒</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>178</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1021,32 +1017,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1120</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1064,7 +1075,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1086,7 +1097,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1102,12 +1113,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1145,52 +1156,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>231</v>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
@@ -1201,62 +1197,57 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Jesus andres</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>@creditorve</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Luis Medina Garcia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 18:23</t>
+          <t>2026-10-27 18:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ider Josue Rodriguez Sabando</t>
+          <t>Jhon Orellana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1266,24 +1257,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>231</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>@crecoselcarmen</t>
+          <t>@crecos.duran</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1296,98 +1298,81 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Jesus andres</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>130</v>
-      </c>
-      <c r="I18" t="inlineStr">
+          <t>@creditorve</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>724</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>A veces</t>
@@ -1395,7 +1380,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas88</t>
+          <t>@crecoselcarmen</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1410,27 +1395,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1440,11 +1425,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1462,200 +1447,226 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>724</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>217</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>@mayra.arteaga212</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L23" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Carlos Steeven</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Independientes</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>(sin agencia)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>@carlosasesordeorvehogar</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>@nouso</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:21</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1665,37 +1676,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>1698</v>
-      </c>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>No</t>
@@ -1706,50 +1702,45 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Isaac Evaristo Wilson bohorquez</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1761,7 +1752,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1771,12 +1762,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>@dannyp109</t>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1786,18 +1777,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>dannyp109</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>280</v>
+        <v>1698</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>No</t>
@@ -1808,56 +1803,50 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL CARMEN</t>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>EliYulexiAlcivar</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>171</v>
-      </c>
-      <c r="I28" t="inlineStr">
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1869,7 +1858,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1879,12 +1868,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1894,15 +1883,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1916,62 +1905,68 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr">
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>171</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1981,19 +1976,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2007,60 +2013,50 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Miguel Coello</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>309</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2072,7 +2068,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2082,7 +2078,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2115,22 +2111,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>@aaronasesorce</t>
+          <t>@macclover23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2140,18 +2136,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>aaronasesorce</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>72</v>
+        <v>309</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>No</t>
@@ -2164,45 +2164,34 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -2215,40 +2204,149 @@
         <v>1</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>72</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>59</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L35"/>
+  <autoFilter ref="A1:L37"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2260,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2336,60 +2434,104 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>@bestpcchillogallo</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Best pc</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Boris Nicolay Toscano</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:34</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>@motopawer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Marcimex</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Motopower</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Iván Quijije Cobeña</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3580,7 +3722,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3600,7 +3742,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3620,7 +3762,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3640,7 +3782,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3660,7 +3802,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3680,7 +3822,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3700,7 +3842,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3720,7 +3862,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3740,7 +3882,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -3760,7 +3902,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -3780,7 +3922,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -3800,7 +3942,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -3820,7 +3962,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -3840,7 +3982,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -3860,7 +4002,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -3880,7 +4022,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -3900,7 +4042,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -3920,7 +4062,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -3940,7 +4082,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -3960,7 +4102,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -3980,7 +4122,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4000,7 +4142,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4020,7 +4162,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4040,7 +4182,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4060,7 +4202,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4080,7 +4222,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4100,7 +4242,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4120,7 +4262,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -4140,7 +4282,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -4160,7 +4302,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -4180,7 +4322,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -4200,7 +4342,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -4220,7 +4362,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -4240,7 +4382,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -4260,7 +4402,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -4280,7 +4422,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -4300,7 +4442,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -4320,7 +4462,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -4335,12 +4477,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -4360,7 +4502,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -4380,7 +4522,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -4400,7 +4542,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -4420,7 +4562,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -4440,7 +4582,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -4460,7 +4602,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -4480,7 +4622,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -4500,7 +4642,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -4520,7 +4662,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -4540,7 +4682,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -4560,7 +4702,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -4575,12 +4717,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -4600,7 +4742,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -4620,7 +4762,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -4640,7 +4782,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -4660,7 +4802,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -4680,7 +4822,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -4700,7 +4842,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -4720,7 +4862,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -4740,7 +4882,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -4760,7 +4902,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -4780,7 +4922,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -4800,7 +4942,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -4820,7 +4962,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -4840,7 +4982,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -4860,7 +5002,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -4880,7 +5022,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -4900,7 +5042,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -4920,7 +5062,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -4940,7 +5082,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -4960,7 +5102,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -4980,7 +5122,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -5000,7 +5142,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -5020,7 +5162,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -5040,7 +5182,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -5060,7 +5202,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -5080,7 +5222,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -5100,7 +5242,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -5120,7 +5262,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -5140,7 +5282,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -5160,7 +5302,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -5180,7 +5322,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -5200,7 +5342,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -5220,7 +5362,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -5240,7 +5382,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -5260,7 +5402,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -5280,7 +5422,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -5300,7 +5442,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -5320,7 +5462,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -5340,7 +5482,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -5360,7 +5502,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -5380,7 +5522,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -5400,7 +5542,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -5420,7 +5562,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -5440,7 +5582,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -5460,7 +5602,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -5480,7 +5622,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -5500,7 +5642,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -5515,12 +5657,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -5535,12 +5677,12 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -5560,7 +5702,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -5580,7 +5722,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -5600,7 +5742,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -5615,12 +5757,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -5635,12 +5777,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -5660,7 +5802,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -5680,7 +5822,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -5700,7 +5842,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -5713,42 +5855,42 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5902,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -5780,7 +5922,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -5800,7 +5942,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -5820,11 +5962,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -5840,7 +5982,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -5860,7 +6002,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -5880,11 +6022,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -5900,11 +6042,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -5915,16 +6057,16 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Independientes</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>INDEPENDIENTES (sin agencia)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -5935,12 +6077,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -5955,12 +6097,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>INDEPENDIENTES (sin agencia)</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -5975,16 +6117,16 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6000,11 +6142,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -6020,11 +6162,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6040,11 +6182,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6055,12 +6197,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -6080,7 +6222,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="C184" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -529,34 +529,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luis plata</t>
+          <t>Fabián Paredes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>CRECOS JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@fabiaparedesd</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Eduardo Paredes</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>455</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -577,40 +588,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boris Nicolay Toscano</t>
+          <t>Luis plata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>@japon.chillogallo</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>84</v>
-      </c>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -631,22 +631,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JEAMPIERRE MORAN</t>
+          <t>Boris Nicolay Toscano</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>@orvejipijapa</t>
+          <t>@japon.chillogallo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -656,22 +656,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OrveHogar Jipijapa</t>
+          <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1016</v>
+        <v>84</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>@sn</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
@@ -684,37 +680,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>JEAMPIERRE MORAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>@orvejipijapa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OrveHogar Jipijapa</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1016</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>@sn</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -732,17 +743,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Digno Gilses</t>
+          <t>Carlos Vargas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -768,105 +779,105 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:32</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Digno Gilses</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:31</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Herrera Llamuca Jenny</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CRECOS POLICENTRO</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>@jennyherrera20</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brian campos</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:28</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arleth Cali</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -879,30 +890,19 @@
           <t>CRECOS NARANJAL</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>182</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -915,12 +915,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -930,19 +930,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Arleth Cali</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>182</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -958,45 +969,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>178</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1012,27 +1012,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>MOTOZONE VINCES</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>@vickman761</t>
+          <t>@karinamorn4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1042,22 +1042,18 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>karii🍒</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1120</v>
+        <v>178</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1075,32 +1071,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1120</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1118,17 +1129,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1161,17 +1172,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1183,7 +1194,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1199,22 +1210,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Eugenia Margarita Tircio Herrera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1226,7 +1237,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1247,47 +1258,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>No</t>
@@ -1298,97 +1294,108 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>231</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Jesus andres</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>ORVE PORTOVIEJO 3</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>@creditorve</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1400,43 +1407,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>130</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>No</t>
@@ -1449,27 +1449,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas1988</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1479,22 +1479,18 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>No</t>
@@ -1512,22 +1508,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@alvarovillegas1988</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1537,18 +1533,22 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Alvaro Villegas</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>217</v>
+        <v>724</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>No</t>
@@ -1559,50 +1559,56 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Mayra Arteaga Intriago</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>@mayra.arteaga212</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr">
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>217</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1614,22 +1620,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Carlos Steeven</t>
+          <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Independientes</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>(sin agencia)</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>@carlosasesordeorvehogar</t>
+          <t>@mayra.arteaga212</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1641,14 +1647,10 @@
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1659,57 +1661,66 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27 18:21</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1719,7 +1730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>ORVE EL CARMEN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1729,12 +1740,12 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>No</t>
@@ -1747,12 +1758,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1762,35 +1773,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>@orveduran</t>
+          <t>@isaacwilaon02</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1803,104 +1799,108 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Christian Sánchez</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ORVE DURAN</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Jordano Zambrano</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>@jordanozambrano</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L28" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>280</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1912,22 +1912,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>@eliyulexialcivar</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1937,15 +1937,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1966,22 +1966,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@eliyulexialcivar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1991,15 +1991,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>EliYulexiAlcivar</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2013,93 +2013,104 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cristina Tenorio</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Mykell Josué Zambrano Yagual</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>CRECOS SALINAS</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>@mykellteve</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Luis Naranjo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2111,47 +2122,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>309</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>No</t>
@@ -2169,32 +2165,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>309</v>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>No</t>
@@ -2212,40 +2223,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2261,12 +2261,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>Aaron Reasco</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>@carlosalbertoterr85</t>
+          <t>@aaronasesorce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2291,15 +2291,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>aaronasesorce</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -2312,41 +2312,96 @@
         <v>1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>59</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L37"/>
+  <autoFilter ref="A1:L38"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2982,7 +3037,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>CRECOS JIPIJAPA</t>
+          <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -3002,7 +3057,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA CONCORDIA</t>
+          <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -3022,7 +3077,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA LIBERTAD</t>
+          <t>CRECOS LA PRENSA</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -3042,7 +3097,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA PRENSA</t>
+          <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -3062,7 +3117,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LA TRONCAL</t>
+          <t>CRECOS LATACUNGA</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -3082,7 +3137,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CRECOS LATACUNGA</t>
+          <t>CRECOS MACHALA</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -3102,7 +3157,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MACHALA</t>
+          <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -3122,7 +3177,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL NORTE</t>
+          <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -3142,7 +3197,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL PACIFICO</t>
+          <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -3162,7 +3217,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL SOL</t>
+          <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -3182,7 +3237,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MALL DEL SUR</t>
+          <t>CRECOS MANTA</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -3202,7 +3257,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MANTA</t>
+          <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -3222,7 +3277,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NACIONES UNIDAS</t>
+          <t>CRECOS NARANJITO</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -3242,7 +3297,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJITO</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -3262,7 +3317,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CRECOS OTAVALO</t>
+          <t>CRECOS PEDERNALES</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -3282,7 +3337,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PEDERNALES</t>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -3302,7 +3357,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+          <t>CRECOS PINAS</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -3322,7 +3377,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PINAS</t>
+          <t>CRECOS PLAYAS</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -3342,7 +3397,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PLAYAS</t>
+          <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -3362,7 +3417,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTAL SHOPPING</t>
+          <t>CRECOS PORTETE</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -3382,7 +3437,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTETE</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -3402,7 +3457,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -3422,7 +3477,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -3442,7 +3497,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -3462,7 +3517,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -3482,7 +3537,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -3502,7 +3557,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3522,7 +3577,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3542,7 +3597,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3562,7 +3617,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3582,7 +3637,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3597,12 +3652,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3622,7 +3677,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3642,7 +3697,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3662,7 +3717,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3682,7 +3737,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3702,7 +3757,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3722,7 +3777,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3742,7 +3797,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3762,7 +3817,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3782,7 +3837,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3802,7 +3857,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3822,7 +3877,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3842,7 +3897,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3862,7 +3917,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3882,7 +3937,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -3902,7 +3957,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -3922,7 +3977,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -3942,7 +3997,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -3962,7 +4017,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -3982,7 +4037,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4002,7 +4057,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4022,7 +4077,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4042,7 +4097,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4062,7 +4117,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4082,7 +4137,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4102,7 +4157,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4122,7 +4177,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4142,7 +4197,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4162,7 +4217,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4182,7 +4237,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4202,7 +4257,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4222,7 +4277,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4242,7 +4297,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4262,7 +4317,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -4282,7 +4337,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -4302,7 +4357,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -4322,7 +4377,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -4342,7 +4397,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -4362,7 +4417,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -4382,7 +4437,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -4402,7 +4457,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -4422,7 +4477,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -4442,7 +4497,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -4457,12 +4512,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -4482,7 +4537,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -4502,7 +4557,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -4522,7 +4577,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -4542,7 +4597,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -4562,7 +4617,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -4582,7 +4637,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -4602,7 +4657,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -4622,7 +4677,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -4642,7 +4697,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -4662,7 +4717,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -4682,7 +4737,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -4697,12 +4752,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -4722,7 +4777,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -4742,7 +4797,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -4762,7 +4817,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -4782,7 +4837,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -4802,7 +4857,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -4822,7 +4877,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -4842,7 +4897,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -4862,7 +4917,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -4882,7 +4937,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -4902,7 +4957,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -4922,7 +4977,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -4942,7 +4997,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -4962,7 +5017,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -4982,7 +5037,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -5002,7 +5057,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -5022,7 +5077,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -5042,7 +5097,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -5062,7 +5117,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -5082,7 +5137,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -5102,7 +5157,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -5122,7 +5177,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -5142,7 +5197,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -5162,7 +5217,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -5182,7 +5237,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -5202,7 +5257,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -5222,7 +5277,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -5242,7 +5297,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -5262,7 +5317,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -5282,7 +5337,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -5302,7 +5357,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -5322,7 +5377,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -5342,7 +5397,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -5362,7 +5417,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -5382,7 +5437,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -5402,7 +5457,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -5422,7 +5477,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -5442,7 +5497,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -5462,7 +5517,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -5482,7 +5537,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -5502,7 +5557,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -5522,7 +5577,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -5542,7 +5597,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -5562,7 +5617,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -5582,7 +5637,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -5602,7 +5657,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -5622,7 +5677,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -5637,12 +5692,12 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -5662,7 +5717,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -5682,7 +5737,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -5702,7 +5757,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -5722,7 +5777,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -5737,12 +5792,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -5762,7 +5817,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -5782,7 +5837,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -5802,7 +5857,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -5822,7 +5877,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -5835,22 +5890,22 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5917,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -5882,7 +5937,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -5902,7 +5957,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -5922,7 +5977,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
       <c r="C169" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -534,22 +534,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fabián Paredes</t>
+          <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRECOS JIPIJAPA</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>@fabiaparedesd</t>
+          <t>@juanconforme3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,18 +559,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eduardo Paredes</t>
+          <t>Juan Conforme</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>455</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>398</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>@juanconfor7</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
@@ -583,22 +583,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luis plata</t>
+          <t>edwin carreño</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>CRECOS MANTA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -626,27 +626,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boris Nicolay Toscano</t>
+          <t>Fabián Paredes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>@japon.chillogallo</t>
+          <t>@fabiaparedesd</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -656,15 +656,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>Eduardo Paredes</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JEAMPIERRE MORAN</t>
+          <t>Luis plata</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -695,37 +695,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>@orvejipijapa</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>OrveHogar Jipijapa</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1016</v>
-      </c>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>@sn</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -738,34 +723,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>Boris Nicolay Toscano</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>@japon.chillogallo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>84</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -781,113 +777,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-10-27 18:34</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JEAMPIERRE MORAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>@orvejipijapa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OrveHogar Jipijapa</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1016</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>@sn</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2026-10-27 18:32</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Digno Gilses</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>(no tiene TikTok)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:31</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Herrera Llamuca Jenny</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>@jennyherrera20</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:30</t>
+          <t>2026-10-27 18:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brian campos</t>
+          <t>Digno Gilses</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -897,12 +903,12 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
@@ -913,68 +919,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:28</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:31</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Herrera Llamuca Jenny</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>182</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+          <t>@jennyherrera20</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1012,27 +1012,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>@karinamorn4</t>
+          <t>@arlethcali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1042,15 +1042,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>karii🍒</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1066,12 +1066,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1081,37 +1081,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Victor Yanzapanta</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1120</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
@@ -1124,34 +1109,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>karii🍒</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>178</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1172,32 +1168,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1120</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
@@ -1215,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1237,7 +1248,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1253,12 +1264,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1296,249 +1307,223 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>2026-10-27 18:25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Eugenia Margarita Tircio Herrera</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>2026-10-27 18:24</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Jhon Orellana</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>231</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Luis Medina Garcia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Jesus andres</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>@creditorve</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>231</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Jesus andres</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>@creditorve</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>130</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>724</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>A veces</t>
@@ -1546,7 +1531,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>@alvarovillegas88</t>
+          <t>@crecoselcarmen</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1561,27 +1546,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>JAPON PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>@ivanquijije09</t>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1591,11 +1576,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1613,200 +1598,226 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>724</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>217</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>@mayra.arteaga212</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="L26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Carlos Steeven</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Independientes</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>(sin agencia)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>@carlosasesordeorvehogar</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>@nouso</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:21</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1816,37 +1827,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>1698</v>
-      </c>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>No</t>
@@ -1857,50 +1853,45 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Isaac Evaristo Wilson bohorquez</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1912,7 +1903,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1922,12 +1913,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
+          <t>ORVE DURAN SHOPPING</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>@dannyp109</t>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1937,78 +1928,76 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>dannyp109</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>280</v>
+        <v>1698</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>EliYulexiAlcivar</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>171</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
+      <c r="L31" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2020,7 +2009,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2030,12 +2019,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
+          <t>ORVE EL QUINCHE</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>@cristinaad67</t>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2045,15 +2034,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -2067,62 +2056,68 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr">
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>171</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2132,19 +2127,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -2158,60 +2164,50 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Miguel Coello</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>309</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2223,7 +2219,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2233,7 +2229,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2266,22 +2262,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>@aaronasesorce</t>
+          <t>@macclover23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2291,18 +2287,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>aaronasesorce</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>72</v>
+        <v>309</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>No</t>
@@ -2315,45 +2315,34 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -2366,42 +2355,152 @@
         <v>1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>72</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>59</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
+  <autoFilter ref="A1:L40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2413,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2489,41 +2588,51 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>@bestpcchillogallo</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Best pc</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Boris Nicolay Toscano</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:34</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
+          <t>@mastermoto.americas</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Master Motos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mastermoto Gye Americas</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>14535</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Juan Gabriel Conforme Marcillo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:36</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2532,61 +2641,363 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>@gmotos.ecuador</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>GMOTOS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Juan Gabriel Conforme Marcillo</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:36</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>@lagangaec</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>La Ganga</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Juan Gabriel Conforme Marcillo</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:36</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>@samadimotosguayaquil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Samandi Guayaquil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Samadi Guayaquil</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3260</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Juan Gabriel Conforme Marcillo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:36</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>@motopowerec</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Motopower</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MotoPowerEc</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>62514</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Juan Gabriel Conforme Marcillo</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:36</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>@teemomeg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OTOM RACING</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Otom Racing Alborada</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>511</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Juan Gabriel Conforme Marcillo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:36</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>@bestpcchillogallo</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Best pc</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Boris Nicolay Toscano</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:34</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>@motopawer</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Marcimex</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Motopower</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Iván Quijije Cobeña</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3237,7 +3648,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CRECOS MANTA</t>
+          <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -3257,7 +3668,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NACIONES UNIDAS</t>
+          <t>CRECOS NARANJITO</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -3277,7 +3688,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CRECOS NARANJITO</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -3297,7 +3708,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CRECOS OTAVALO</t>
+          <t>CRECOS PEDERNALES</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -3317,7 +3728,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PEDERNALES</t>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -3337,7 +3748,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+          <t>CRECOS PINAS</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -3357,7 +3768,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PINAS</t>
+          <t>CRECOS PLAYAS</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -3377,7 +3788,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PLAYAS</t>
+          <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
@@ -3397,7 +3808,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTAL SHOPPING</t>
+          <t>CRECOS PORTETE</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -3417,7 +3828,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTETE</t>
+          <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -3437,7 +3848,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 2</t>
+          <t>CRECOS QUEVEDO</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -3457,7 +3868,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUEVEDO</t>
+          <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -3477,7 +3888,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CRECOS QUICENTRO SUR</t>
+          <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -3497,7 +3908,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
+          <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -3517,7 +3928,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CRECOS RIOCENTRO SUR</t>
+          <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -3537,7 +3948,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SAN VICENTE</t>
+          <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -3557,7 +3968,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANGOLQUI</t>
+          <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -3577,7 +3988,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTA ROSA</t>
+          <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -3597,7 +4008,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -3617,7 +4028,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
+          <t>CRECOS TUMBACO</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -3632,12 +4043,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CRECOS TUMBACO</t>
+          <t>JAPON AMBATO</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -3657,7 +4068,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>JAPON AMBATO</t>
+          <t>JAPON BABAHOYO</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -3677,7 +4088,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>JAPON BABAHOYO</t>
+          <t>JAPON CALDERON</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -3697,7 +4108,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>JAPON CALDERON</t>
+          <t>JAPON CARAPUNGO</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -3717,7 +4128,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JAPON CARAPUNGO</t>
+          <t>JAPON CAYAMBE</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -3737,7 +4148,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>JAPON CAYAMBE</t>
+          <t>JAPON CHONE</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -3757,7 +4168,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>JAPON CHONE</t>
+          <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -3777,7 +4188,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
+          <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -3797,7 +4208,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>JAPON CONDADO SHOPPING</t>
+          <t>JAPON CUENCA</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -3817,7 +4228,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>JAPON CUENCA</t>
+          <t>JAPON EL QUINCHE</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -3837,7 +4248,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL QUINCHE</t>
+          <t>JAPON EL RECREO 1</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
@@ -3857,7 +4268,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 1</t>
+          <t>JAPON EL RECREO 2</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -3877,7 +4288,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>JAPON EL RECREO 2</t>
+          <t>JAPON ESMERALDAS</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -3897,7 +4308,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>JAPON ESMERALDAS</t>
+          <t>JAPON GUAMANI</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -3917,7 +4328,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>JAPON GUAMANI</t>
+          <t>JAPON IBARRA 1</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -3937,7 +4348,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 1</t>
+          <t>JAPON IBARRA 2</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -3957,7 +4368,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>JAPON IBARRA 2</t>
+          <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -3977,7 +4388,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
+          <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
@@ -3997,7 +4408,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA CONCORDIA</t>
+          <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -4017,7 +4428,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA LIBERTAD</t>
+          <t>JAPON LA PRENSA</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
@@ -4037,7 +4448,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>JAPON LA PRENSA</t>
+          <t>JAPON LATACUNGA</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -4057,7 +4468,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>JAPON LATACUNGA</t>
+          <t>JAPON LOJA</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -4077,7 +4488,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>JAPON LOJA</t>
+          <t>JAPON MACHACHI</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -4097,7 +4508,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHACHI</t>
+          <t>JAPON MACHALA</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -4117,7 +4528,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>JAPON MACHALA</t>
+          <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -4137,7 +4548,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL NORTE</t>
+          <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -4157,7 +4568,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>JAPON MALL DEL PACIFICO</t>
+          <t>JAPON MANTA 1</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
@@ -4177,7 +4588,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 1</t>
+          <t>JAPON MANTA 2</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
@@ -4197,7 +4608,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>JAPON MANTA 2</t>
+          <t>JAPON MILAGRO</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
@@ -4217,7 +4628,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>JAPON MILAGRO</t>
+          <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -4237,7 +4648,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>JAPON NACIONES UNIDAS</t>
+          <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
@@ -4257,7 +4668,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
+          <t>JAPON PASAJE</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -4277,7 +4688,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>JAPON PASAJE</t>
+          <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
@@ -4297,7 +4708,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>JAPON PORTOVIEJO 2</t>
+          <t>JAPON QUEVEDO</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
@@ -4317,7 +4728,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUEVEDO</t>
+          <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
@@ -4337,7 +4748,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>JAPON QUICENTRO SUR</t>
+          <t>JAPON RIOBAMBA</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
@@ -4357,7 +4768,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>JAPON RIOBAMBA</t>
+          <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -4377,7 +4788,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>JAPON SAN ANTONIO</t>
+          <t>JAPON SANGOLQUI</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -4397,7 +4808,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANGOLQUI</t>
+          <t>JAPON SANTA ROSA</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -4417,7 +4828,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTA ROSA</t>
+          <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
@@ -4437,7 +4848,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 1</t>
+          <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
@@ -4457,7 +4868,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JAPON SANTO DOMINGO 2</t>
+          <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
@@ -4477,7 +4888,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>JAPON SCALA SHOPPING</t>
+          <t>JAPON TUMBACO</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
@@ -4492,12 +4903,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>JAPON TUMBACO</t>
+          <t>MOTOZONE AMBATO</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
@@ -4517,7 +4928,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE AMBATO</t>
+          <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -4537,7 +4948,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE BABAHOYO</t>
+          <t>MOTOZONE EL COCA</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
@@ -4557,7 +4968,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE EL COCA</t>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
@@ -4577,7 +4988,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+          <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -4597,7 +5008,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA LIBERTAD</t>
+          <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
@@ -4617,7 +5028,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE LA PRENSA</t>
+          <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
@@ -4637,7 +5048,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE MILAGRO</t>
+          <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
@@ -4657,7 +5068,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE PORTOVIEJO</t>
+          <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -4677,7 +5088,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -4697,7 +5108,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
+          <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -4717,7 +5128,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE TUMBACO</t>
+          <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
@@ -4732,12 +5143,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MOTOZONE VENTANAS</t>
+          <t>ORVE ALBORADA</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
@@ -4757,7 +5168,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>ORVE ALBORADA</t>
+          <t>ORVE AMBATO</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
@@ -4777,7 +5188,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>ORVE AMBATO</t>
+          <t>ORVE BABAHOYO</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
@@ -4797,7 +5208,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>ORVE BABAHOYO</t>
+          <t>ORVE BALZAR</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
@@ -4817,7 +5228,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>ORVE BALZAR</t>
+          <t>ORVE CALCETA</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
@@ -4837,7 +5248,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALCETA</t>
+          <t>ORVE CALDERON</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -4857,7 +5268,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>ORVE CALDERON</t>
+          <t>ORVE CARAPUNGO</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
@@ -4877,7 +5288,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ORVE CARAPUNGO</t>
+          <t>ORVE CAYAMBE</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -4897,7 +5308,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ORVE CAYAMBE</t>
+          <t>ORVE CHONE</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
@@ -4917,7 +5328,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ORVE CHONE</t>
+          <t>ORVE CONDADO SHOPPING</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
@@ -4937,7 +5348,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ORVE CONDADO SHOPPING</t>
+          <t>ORVE DAULE</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -4957,7 +5368,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ORVE DAULE</t>
+          <t>ORVE EL ARENAL</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -4977,7 +5388,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL ARENAL</t>
+          <t>ORVE EL RECREO 2</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
@@ -4997,7 +5408,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 2</t>
+          <t>ORVE EL RECREO 3</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
@@ -5017,7 +5428,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 3</t>
+          <t>ORVE ESMERALDAS</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
@@ -5037,7 +5448,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ORVE ESMERALDAS</t>
+          <t>ORVE GUAMANI</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
@@ -5057,7 +5468,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUAMANI</t>
+          <t>ORVE GUARANDA</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
@@ -5077,7 +5488,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ORVE GUARANDA</t>
+          <t>ORVE IBARRA 1</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
@@ -5097,7 +5508,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>ORVE IBARRA 1</t>
+          <t>ORVE LA CONCORDIA</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -5117,7 +5528,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA CONCORDIA</t>
+          <t>ORVE LA LIBERTAD</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -5137,7 +5548,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA LIBERTAD</t>
+          <t>ORVE LA PRENSA</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
@@ -5157,7 +5568,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ORVE LA PRENSA</t>
+          <t>ORVE LAGO AGRIO</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
@@ -5177,7 +5588,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>ORVE LAGO AGRIO</t>
+          <t>ORVE LATACUNGA 1</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -5197,7 +5608,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ORVE LATACUNGA 1</t>
+          <t>ORVE LOJA</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
@@ -5217,7 +5628,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ORVE LOJA</t>
+          <t>ORVE MACHACHI</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -5237,7 +5648,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHACHI</t>
+          <t>ORVE MACHALA 2</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
@@ -5257,7 +5668,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>ORVE MACHALA 2</t>
+          <t>ORVE MALL DEL SUR</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
@@ -5277,7 +5688,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ORVE MALL DEL SUR</t>
+          <t>ORVE MANTA 1</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
@@ -5297,7 +5708,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>ORVE MANTA 1</t>
+          <t>ORVE MILAGRO</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
@@ -5317,7 +5728,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ORVE MILAGRO</t>
+          <t>ORVE NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
@@ -5337,7 +5748,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>ORVE NACIONES UNIDAS</t>
+          <t>ORVE NARANJITO</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
@@ -5357,7 +5768,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ORVE NARANJITO</t>
+          <t>ORVE NUEVA AURORA</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -5377,7 +5788,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ORVE NUEVA AURORA</t>
+          <t>ORVE PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -5397,7 +5808,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
+          <t>ORVE PEDERNALES</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
@@ -5417,7 +5828,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ORVE PEDERNALES</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
@@ -5437,7 +5848,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ORVE PIFO</t>
+          <t>ORVE PINAS</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -5457,7 +5868,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ORVE PINAS</t>
+          <t>ORVE PORTETE</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -5477,7 +5888,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTETE</t>
+          <t>ORVE PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -5497,7 +5908,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>ORVE PORTOVIEJO 1</t>
+          <t>ORVE QUEVEDO</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
@@ -5517,7 +5928,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUEVEDO</t>
+          <t>ORVE QUICENTRO SUR</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -5537,7 +5948,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUICENTRO SUR</t>
+          <t>ORVE QUININDE</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
@@ -5557,7 +5968,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ORVE QUININDE</t>
+          <t>ORVE RIOBAMBA 1</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -5577,7 +5988,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ORVE RIOBAMBA 1</t>
+          <t>ORVE SANTA ANA</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -5597,7 +6008,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA ANA</t>
+          <t>ORVE SANTA LUCIA</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
@@ -5617,7 +6028,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTA LUCIA</t>
+          <t>ORVE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
@@ -5637,7 +6048,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ORVE SANTO DOMINGO</t>
+          <t>ORVE TUMBACO</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -5657,7 +6068,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>ORVE TUMBACO</t>
+          <t>ORVE VINCES</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
@@ -5672,12 +6083,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Pagamenos</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ORVE VINCES</t>
+          <t>PAGA MENOS CHONE</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
@@ -5697,7 +6108,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS CHONE</t>
+          <t>PAGA MENOS DAULE</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -5717,7 +6128,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS DAULE</t>
+          <t>PAGA MENOS LA LIBERTAD</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -5737,7 +6148,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
@@ -5757,7 +6168,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+          <t>PAGA MENOS PORTOVIEJO</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -5772,12 +6183,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Pagamenos</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
+          <t>SAMSUNG CITY MALL</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
@@ -5797,7 +6208,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG CITY MALL</t>
+          <t>SAMSUNG DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -5817,7 +6228,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
+          <t>SAMSUNG EL DORADO</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
@@ -5837,7 +6248,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG EL DORADO</t>
+          <t>SAMSUNG MALL DEL SOL</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
@@ -5857,7 +6268,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>SAMSUNG MALL DEL SOL</t>
+          <t>SAMSUNG QUICENTRO NORTE</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -5870,22 +6281,22 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5897,7 +6308,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS DURAN SHOPPING</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -5917,7 +6328,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -5937,7 +6348,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -5957,7 +6368,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -5977,7 +6388,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRECOS JIPIJAPA</t>
+          <t>CRECOS MANTA</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -6201,7 +6612,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,8 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -527,68 +527,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:36</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Juan Gabriel Conforme Marcillo</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>@juanconforme3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Juan Conforme</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>398</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>@juanconfor7</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:38</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Michael Méndez</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>@crecossantodomingo2</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:36</t>
+          <t>2026-10-27 18:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>edwin carreño</t>
+          <t>Deyra Maricela Carbajal Valle</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,7 +592,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRECOS MANTA</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,10 +604,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>@deyracarbajal</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
@@ -626,12 +624,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 18:36</t>
+          <t>2026-10-27 18:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fabián Paredes</t>
+          <t>franklin Chancay Tumbaco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,9 +642,9 @@
           <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>@fabiaparedesd</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>@franklinchancay</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -656,11 +654,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eduardo Paredes</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>455</v>
+        <v>125</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -680,37 +678,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luis plata</t>
+          <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>@juanconforme3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Juan Conforme</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>398</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>@juanconfor7</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
@@ -723,45 +732,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boris Nicolay Toscano</t>
+          <t>edwin carreño</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>@japon.chillogallo</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>84</v>
-      </c>
+          <t>CRECOS MANTA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -777,27 +775,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JEAMPIERRE MORAN</t>
+          <t>Fabián Paredes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>@orvejipijapa</t>
+          <t>CRECOS JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>@fabiaparedesd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -807,22 +805,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OrveHogar Jipijapa</t>
+          <t>Eduardo Paredes</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1016</v>
+        <v>455</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>@sn</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
@@ -835,22 +829,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>Luis plata</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>ORVE CUENCA 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -862,7 +856,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -878,34 +872,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Digno Gilses</t>
+          <t>Boris Nicolay Toscano</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>@japon.chillogallo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>84</v>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -919,62 +924,72 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:31</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Herrera Llamuca Jenny</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>@jennyherrera20</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:34</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JEAMPIERRE MORAN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>@orvejipijapa</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OrveHogar Jipijapa</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1016</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>@sn</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:30</t>
+          <t>2026-10-27 18:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brian campos</t>
+          <t>Carlos Vargas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -984,7 +999,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -994,12 +1009,12 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1012,42 +1027,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27 18:28</t>
+          <t>2026-10-27 18:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arleth Cali</t>
+          <t>Digno Gilses</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>182</v>
-      </c>
+          <t>ORVE EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>A veces</t>
@@ -1064,93 +1068,87 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:27</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jessica samaniego</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CRECOS MILAGRO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:31</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Herrera Llamuca Jenny</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>@jennyherrera20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
+      <c r="L13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>karii🍒</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>178</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1163,12 +1161,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1178,12 +1176,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1193,22 +1191,18 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1120</v>
+        <v>182</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
@@ -1221,22 +1215,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,12 +1258,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1279,19 +1273,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>karii🍒</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>178</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1312,32 +1317,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1120</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1350,22 +1370,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
+          <t>ORVE PLAYAS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1393,128 +1413,108 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jhon Orellana</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>231</v>
-      </c>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eugenia Margarita Tircio Herrera</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Jesus andres</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>@creditorve</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 18:23</t>
+          <t>2026-10-27 18:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ider Josue Rodriguez Sabando</t>
+          <t>Luis Medina Garcia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>MOTOZONE PLAYAS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1526,14 +1526,10 @@
       <c r="G22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>No</t>
@@ -1546,266 +1542,265 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>231</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>130</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Jesus andres</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>@creditorve</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>724</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-10-27 18:23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ider Josue Rodriguez Sabando</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Jofre Miguel Vélez Marcillo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>@jofrevelez22</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Jofre Vélez</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>130</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Iván Quijije Cobeña</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>@ivanquijije09</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Iván93 😎</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>217</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>724</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Mayra Arteaga Intriago</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>@mayra.arteaga212</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Carlos Steeven</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Independientes</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>(sin agencia)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>@carlosasesordeorvehogar</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>@nouso</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1817,29 +1812,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Edson Velez</t>
+          <t>Iván Quijije Cobeña</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>217</v>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1853,163 +1859,157 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:21</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Mayra Arteaga Intriago</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>@mayra.arteaga212</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Steeven</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Independientes</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>(sin agencia)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>@carlosasesordeorvehogar</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>@nouso</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Edson Velez</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>(no tiene TikTok)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Christian Sánchez</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Isaac Evaristo Wilson bohorquez</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2019,33 +2019,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>dannyp109</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>280</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>No</t>
@@ -2063,22 +2052,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2088,157 +2077,172 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>EliYulexiAlcivar</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>171</v>
+        <v>1698</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="L34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Cristina Tenorio</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DANNY DAVID PINCAY PONCE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ORVE SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>@cristinaad67</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Cristina AD</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>dannyp109</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>280</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>171</v>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>No</t>
@@ -2257,27 +2261,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Miguel Coello</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2287,22 +2291,18 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>Cristina AD</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>No</t>
@@ -2313,45 +2313,50 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>César Roberto Maldonado Carlozama</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ORVE OTAVALO</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
+      <c r="L38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2363,40 +2368,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>aaronasesorce</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>72</v>
-      </c>
+          <t>ORVE 9 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -2412,95 +2406,253 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Miguel Coello</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Miguel Angel</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>309</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>César Roberto Maldonado Carlozama</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>72</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>2026-10-27 18:18</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Carlos Terreros</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>CRECOS CUENCA</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>@carlosalbertoterr85</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Carlos</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H43" t="n">
         <v>59</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="L43" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2512,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2586,409 +2738,456 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>@point</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Lives</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Deyra Maricela Carbajal Valle</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS OTAVALO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:38</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>@mastermoto.americas</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Master Motos</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Mastermoto Gye Americas</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>14535</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>@gmotos.ecuador</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>GMOTOS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>@lagangaec</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>La Ganga</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>@samadimotosguayaquil</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Samandi Guayaquil</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Samadi Guayaquil</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>3260</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>@motopowerec</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Motopower</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>MotoPowerEc</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>62514</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>@teemomeg</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>OTOM RACING</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Otom Racing Alborada</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>511</v>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>@bestpcchillogallo</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Best pc</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Boris Nicolay Toscano</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 18:34</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>@motopawer</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Marcimex</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Motopower</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Iván Quijije Cobeña</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -2998,6 +3197,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3041,3242 +3241,3242 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS OTAVALO</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PEDERNALES</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PEDERNALES</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PIAZZA VIA A LA COSTA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PIAZZA VIA A LA COSTA</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PINAS</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PINAS</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PLAYAS</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PLAYAS</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTAL SHOPPING</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTAL SHOPPING</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTETE</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTETE</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 2</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 2</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS RIOCENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS RIOCENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS RIOCENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS RIOCENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SAN VICENTE</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS SANTO DOMINGO 1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANTO DOMINGO 1</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CRECOS TUMBACO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>JAPON AMBATO</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>CRECOS TUMBACO</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>JAPON BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>JAPON AMBATO</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CALDERON</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>JAPON BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CALDERON</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CHONE</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>JAPON COMITE DEL PUEBLO</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CHONE</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>JAPON COMITE DEL PUEBLO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>JAPON CUENCA</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>JAPON CUENCA</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL RECREO 1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>JAPON EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>JAPON ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>JAPON EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>JAPON GUAMANI</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>JAPON ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>JAPON IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>JAPON GUAMANI</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>JAPON IBARRA 2</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>JAPON IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>JAPON ISLA MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>JAPON IBARRA 2</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>JAPON ISLA MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LATACUNGA</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>JAPON LOJA</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LATACUNGA</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MACHACHI</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>JAPON LOJA</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MACHALA</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MACHACHI</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MALL DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MACHALA</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MALL DEL PACIFICO</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MALL DEL NORTE</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MANTA 1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MALL DEL PACIFICO</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MANTA 2</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MANTA 1</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>JAPON MILAGRO</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MANTA 2</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>JAPON NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>JAPON MILAGRO</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>JAPON NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PASAJE</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>JAPON PORTOVIEJO 2</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PASAJE</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>JAPON QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 2</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>JAPON QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>JAPON QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>JAPON RIOBAMBA</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>JAPON QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>JAPON RIOBAMBA</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SAN ANTONIO</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTA ROSA</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 1</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>JAPON SCALA SHOPPING</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>JAPON TUMBACO</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>JAPON SCALA SHOPPING</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE AMBATO</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>JAPON TUMBACO</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE AMBATO</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL COCA</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE ISLA QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL COCA</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE ISLA QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>MOTOZONE VENTANAS</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ORVE ALBORADA</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>MOTOZONE VENTANAS</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ORVE AMBATO</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>ORVE ALBORADA</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ORVE BABAHOYO</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>ORVE AMBATO</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ORVE BALZAR</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>ORVE BABAHOYO</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CALCETA</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>ORVE BALZAR</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CALDERON</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CALCETA</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CARAPUNGO</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CALDERON</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CAYAMBE</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CARAPUNGO</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CHONE</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CAYAMBE</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ORVE CONDADO SHOPPING</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CHONE</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ORVE DAULE</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>ORVE CONDADO SHOPPING</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL ARENAL</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>ORVE DAULE</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 2</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL ARENAL</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ORVE EL RECREO 3</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 2</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ORVE ESMERALDAS</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 3</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ORVE GUAMANI</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>ORVE ESMERALDAS</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ORVE GUARANDA</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>ORVE GUAMANI</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ORVE IBARRA 1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>ORVE GUARANDA</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA CONCORDIA</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>ORVE IBARRA 1</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA CONCORDIA</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LA PRENSA</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LAGO AGRIO</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LA PRENSA</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LATACUNGA 1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LAGO AGRIO</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ORVE LOJA</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LATACUNGA 1</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MACHACHI</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>ORVE LOJA</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MACHALA 2</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MACHACHI</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MALL DEL SUR</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MACHALA 2</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MANTA 1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MALL DEL SUR</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ORVE MILAGRO</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MANTA 1</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>ORVE MILAGRO</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NARANJITO</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>ORVE NUEVA AURORA</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NARANJITO</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>ORVE NUEVA AURORA</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PEDERNALES</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PIFO</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PEDERNALES</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PINAS</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PIFO</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTETE</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PINAS</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTETE</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUEVEDO</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUICENTRO SUR</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUEVEDO</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>ORVE QUININDE</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUICENTRO SUR</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>ORVE RIOBAMBA 1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>ORVE QUININDE</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTA ANA</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>ORVE RIOBAMBA 1</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTA ANA</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>ORVE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTA LUCIA</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>ORVE TUMBACO</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>ORVE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>ORVE VINCES</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>ORVE TUMBACO</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS CHONE</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>ORVE VINCES</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Pagamenos</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS DAULE</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS CHONE</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS DAULE</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Pagamenos</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>PAGA MENOS PORTOVIEJO</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG CITY MALL</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>Pagamenos</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>PAGA MENOS PORTOVIEJO</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG CITY MALL</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG EL DORADO</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG MALL DEL SOL</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG EL DORADO</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG QUICENTRO NORTE</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG MALL DEL SOL</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>SAMSUNG QUICENTRO NORTE</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Sin respuestas</t>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6488,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
+          <t>CRECOS EL CARMEN</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -6308,7 +6508,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CRECOS DURAN SHOPPING</t>
+          <t>CRECOS EL GUASMO</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -6328,11 +6528,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CRECOS EL CARMEN</t>
+          <t>CRECOS JIPIJAPA</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -6348,7 +6548,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
+          <t>CRECOS MANTA</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -6368,7 +6568,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CRECOS JIPIJAPA</t>
+          <t>CRECOS MILAGRO</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -6388,11 +6588,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRECOS MANTA</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6408,7 +6608,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS OTAVALO</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -6428,11 +6628,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>CRECOS PARQUE CALIFORNIA</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -6448,11 +6648,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
+          <t>CRECOS POLICENTRO</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -6468,11 +6668,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
+          <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6488,11 +6688,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
+          <t>CRECOS SALINAS</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6508,7 +6708,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRECOS SALINAS</t>
+          <t>CRECOS SANTO DOMINGO 2</t>
         </is>
       </c>
       <c r="C175" t="n">

--- a/data/encuesta/Encuesta_TikTok_Cresa.xlsx
+++ b/data/encuesta/Encuesta_TikTok_Cresa.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Avance por agencia" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuentas Cresa'!$A$1:$L$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Competencia'!$A$1:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avance por agencia'!$A$1:$D$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,8 +79,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -527,72 +527,82 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:38</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Michael Méndez</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>CRECOS SANTO DOMINGO 2</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>@crecossantodomingo2</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:39</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Diego Pico</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CRECOS MANTA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>@crecosmanta</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Crecos Manta</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>189</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>@crecosmanta</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 18:38</t>
+          <t>2026-10-27 18:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deyra Maricela Carbajal Valle</t>
+          <t>Belen Burbano</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRECOS OTAVALO</t>
+          <t>ORVE PIFO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,120 +614,103 @@
       <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:38</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Méndez</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SANTO DOMINGO 2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>@crecossantodomingo2</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>@deyracarbajal</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:37</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>franklin Chancay Tumbaco</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CRECOS JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>@franklinchancay</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Franklin</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>125</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:36</t>
+          <t>2026-10-27 18:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Juan Gabriel Conforme Marcillo</t>
+          <t>Deyra Maricela Carbajal Valle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>@juanconforme3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Juan Conforme</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>398</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>@juanconfor7</t>
+          <t>CRECOS OTAVALO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>@deyracarbajal</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -732,12 +725,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 18:36</t>
+          <t>2026-10-27 18:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>edwin carreño</t>
+          <t>franklin Chancay Tumbaco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -747,19 +740,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRECOS MANTA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>CRECOS JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>@franklinchancay</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Franklin</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>125</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -780,22 +784,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fabián Paredes</t>
+          <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRECOS JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>@fabiaparedesd</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>@juanconforme3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -805,18 +809,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eduardo Paredes</t>
+          <t>Juan Conforme</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>455</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>398</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>@juanconfor7</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
@@ -829,22 +833,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luis plata</t>
+          <t>edwin carreño</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ORVE CUENCA 1</t>
+          <t>CRECOS MANTA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -872,27 +876,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27 18:34</t>
+          <t>2026-10-27 18:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Boris Nicolay Toscano</t>
+          <t>Fabián Paredes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>@japon.chillogallo</t>
+          <t>CRECOS JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>@fabiaparedesd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -902,15 +906,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JAPON CHILLOGALLO</t>
+          <t>Eduardo Paredes</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -931,7 +935,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JEAMPIERRE MORAN</t>
+          <t>Luis plata</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -941,37 +945,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ORVE JIPIJAPA</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>@orvejipijapa</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>OrveHogar Jipijapa</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1016</v>
-      </c>
+          <t>ORVE CUENCA 1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>@sn</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
@@ -984,34 +973,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27 18:32</t>
+          <t>2026-10-27 18:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carlos Vargas</t>
+          <t>Boris Nicolay Toscano</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>@japon.chillogallo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>JAPON CHILLOGALLO</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>84</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>A veces</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1027,113 +1027,123 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-10-27 18:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JEAMPIERRE MORAN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ORVE JIPIJAPA</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>@orvejipijapa</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OrveHogar Jipijapa</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1016</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>@sn</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2026-10-27 18:32</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Digno Gilses</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ORVE EL RECREO 1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Carlos Vargas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>(no tiene TikTok)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:31</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Herrera Llamuca Jenny</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>CRECOS POLICENTRO</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>@jennyherrera20</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27 18:30</t>
+          <t>2026-10-27 18:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brian campos</t>
+          <t>Digno Gilses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRECOS NARANJAL</t>
+          <t>ORVE EL RECREO 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1143,12 +1153,12 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>@no</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1159,68 +1169,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:28</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CRECOS NARANJAL</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>@arlethcali</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Arleth Cali</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>182</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:31</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Herrera Llamuca Jenny</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS POLICENTRO</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>@jennyherrera20</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27 18:27</t>
+          <t>2026-10-27 18:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jessica samaniego</t>
+          <t>Brian campos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1230,7 +1234,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRECOS MILAGRO</t>
+          <t>CRECOS NARANJAL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1240,12 +1244,12 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>@no</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>No</t>
@@ -1258,27 +1262,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27 18:26</t>
+          <t>2026-10-27 18:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karina Morán</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MOTOZONE VINCES</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>@karinamorn4</t>
+          <t>CRECOS NARANJAL</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>@arlethcali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1288,15 +1292,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>karii🍒</t>
+          <t>Arleth Cali</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1312,12 +1316,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Victor Yanzapanta</t>
+          <t>Jessica samaniego</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1327,37 +1331,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRECOS EL GUASMO</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Victor Yanzapanta</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1120</v>
-      </c>
+          <t>CRECOS MILAGRO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>@vickman761</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
@@ -1370,34 +1359,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27 18:25</t>
+          <t>2026-10-27 18:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valeria cepeda</t>
+          <t>Karina Morán</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orve Hogar</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>MOTOZONE VINCES</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>@karinamorn4</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>karii🍒</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>178</v>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1418,32 +1418,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rosa Sánchez</t>
+          <t>Victor Yanzapanta</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MOTOZONE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>CRECOS EL GUASMO</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Victor Yanzapanta</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1120</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>@vickman761</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>No</t>
@@ -1461,7 +1476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eugenia Margarita Tircio Herrera</t>
+          <t>Valeria cepeda</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1483,7 +1498,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1499,12 +1514,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27 18:24</t>
+          <t>2026-10-27 18:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luis Medina Garcia</t>
+          <t>Rosa Sánchez</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1542,257 +1557,231 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-10-27 18:25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Eugenia Margarita Tircio Herrera</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-10-27 18:24</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Jhon Orellana</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CRECOS DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CRECOS DURÁN SHOPPING</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>231</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>@crecos.duran</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Luis Medina Garcia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MOTOZONE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Jesus andres</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>ORVE PORTOVIEJO 3</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>@creditorve</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-10-27 18:24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jhon Orellana</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRECOS DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CRECOS DURÁN SHOPPING</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>231</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>@crecos.duran</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>2026-10-27 18:23</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ider Josue Rodriguez Sabando</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CRECOS EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>@crecoselcarmen</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Jesus andres</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PORTOVIEJO 3</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>@creditorve</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:23</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Jofre Miguel Vélez Marcillo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>JAPON PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>@jofrevelez22</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Jofre Vélez</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>130</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alvaro Villegas</t>
+          <t>Ider Josue Rodriguez Sabando</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Motozone</t>
+          <t>Crecos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>@alvarovillegas1988</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Alvaro Villegas</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>724</v>
-      </c>
+          <t>CRECOS EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>@alvarovillegas88</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>@crecoselcarmen</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1807,27 +1796,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27 18:22</t>
+          <t>2026-10-27 18:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Iván Quijije Cobeña</t>
+          <t>Jofre Miguel Vélez Marcillo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>@ivanquijije09</t>
+          <t>JAPON PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>@jofrevelez22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1837,11 +1826,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Iván93 😎</t>
+          <t>Jofre Vélez</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1859,200 +1848,226 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas1988</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alvaro Villegas</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>724</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>@alvarovillegas88</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Iván Quijije Cobeña</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>@ivanquijije09</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Iván93 😎</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>217</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:22</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Mayra Arteaga Intriago</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>@mayra.arteaga212</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L29" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="L31" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Carlos Steeven</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Independientes</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>(sin agencia)</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>@carlosasesordeorvehogar</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Sí, seguido</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>@nouso</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:22</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Edson Velez</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ORVE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:21</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Isaac Evaristo Wilson bohorquez</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Orve Hogar</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ORVE PLAYAS</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>@isaacwilaon02</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-27 18:20</t>
+          <t>2026-10-27 18:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Christian Sánchez</t>
+          <t>Edson Velez</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2062,37 +2077,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ORVE DURAN SHOPPING</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ORVE DURAN</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>1698</v>
-      </c>
+          <t>ORVE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>@orveduran</t>
-        </is>
-      </c>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>No</t>
@@ -2103,50 +2103,45 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Jordano Zambrano</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>CRECOS PORTOVIEJO 1</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>@jordanozambrano</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Isaac Evaristo Wilson bohorquez</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Orve Hogar</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ORVE PLAYAS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>@isaacwilaon02</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="L34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2158,7 +2153,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DANNY DAVID PINCAY PONCE</t>
+          <t>Christian Sánchez</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2168,12 +2163,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ORVE EL QUINCHE</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>@dannyp109</t>
+          <t>ORVE DURAN SHOPPING</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2183,78 +2178,76 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>dannyp109</t>
+          <t>ORVE DURAN</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>280</v>
+        <v>1698</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>@orveduran</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Jordano Zambrano</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS PORTOVIEJO 1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>@jordanozambrano</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
           <t>A veces</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:20</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Eliana Yulexi Alcivar Zambrano</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>MOTOZONE EL CARMEN</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>@eliyulexialcivar</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>EliYulexiAlcivar</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>171</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
+      <c r="L36" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2266,7 +2259,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cristina Tenorio</t>
+          <t>DANNY DAVID PINCAY PONCE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2276,12 +2269,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ORVE SANGOLQUI</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>@cristinaad67</t>
+          <t>ORVE EL QUINCHE</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>@dannyp109</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2291,15 +2284,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cristina AD</t>
+          <t>dannyp109</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>A veces</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -2313,62 +2306,68 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2026-10-27 18:20</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Mykell Josué Zambrano Yagual</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>CRECOS SALINAS</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>@mykellteve</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>NO EXISTE – revisar</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Eliana Yulexi Alcivar Zambrano</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Motozone</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MOTOZONE EL CARMEN</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>@eliyulexialcivar</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>EliYulexiAlcivar</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>171</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L38" s="2" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-27 18:19</t>
+          <t>2026-10-27 18:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Luis Naranjo</t>
+          <t>Cristina Tenorio</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2378,19 +2377,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ORVE 9 DE OCTUBRE</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>(no tiene TikTok)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>ORVE SANGOLQUI</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>@cristinaad67</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cristina AD</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, seguido</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -2404,60 +2414,50 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-10-27 18:19</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Miguel Coello</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Motozone</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>MOTOZONE PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>@macclover23</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Miguel Angel</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>309</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Sí, seguido</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>@miguel_angel_c28</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:20</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Mykell Josué Zambrano Yagual</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>CRECOS SALINAS</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>@mykellteve</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>César Roberto Maldonado Carlozama</t>
+          <t>Luis Naranjo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ORVE OTAVALO</t>
+          <t>ORVE 9 DE OCTUBRE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aaron Reasco</t>
+          <t>Miguel Coello</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Motozone</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRECOS PARQUE CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>@aaronasesorce</t>
+          <t>MOTOZONE PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>@macclover23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2537,18 +2537,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>aaronasesorce</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>72</v>
+        <v>309</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>A veces</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>@miguel_angel_c28</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>No</t>
@@ -2561,45 +2565,34 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-27 18:18</t>
+          <t>2026-10-27 18:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Carlos Terreros</t>
+          <t>César Roberto Maldonado Carlozama</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Crecos</t>
+          <t>Orve Hogar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRECOS CUENCA</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>@carlosalbertoterr85</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>59</v>
-      </c>
+          <t>ORVE OTAVALO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(no tiene TikTok)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Sí, seguido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -2612,47 +2605,157 @@
         <v>1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:19</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Aaron Reasco</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CRECOS PARQUE CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>@aaronasesorce</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>aaronasesorce</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>72</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>A veces</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Carlos Terreros</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CRECOS CUENCA</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>@carlosalbertoterr85</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>59</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sí, seguido</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2664,7 +2767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2738,456 +2841,503 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>@laganga</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Marcimex</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>NO EXISTE – revisar</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Belen Burbano</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>ORVE PIFO</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:39</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>@point</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Point</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Deyra Maricela Carbajal Valle</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>CRECOS OTAVALO</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:38</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>@mastermoto.americas</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Master Motos</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Mastermoto Gye Americas</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>14535</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>@gmotos.ecuador</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>GMOTOS</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>@lagangaec</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>La Ganga</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>@samadimotosguayaquil</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Samandi Guayaquil</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Samadi Guayaquil</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>3260</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>@motopowerec</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Motopower</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>MotoPowerEc</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>62514</v>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>@teemomeg</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>OTOM RACING</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Otom Racing Alborada</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>511</v>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Juan Gabriel Conforme Marcillo</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>MOTOZONE PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-10-27 18:36</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>@bestpcchillogallo</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Best pc</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>NO EXISTE – revisar</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Boris Nicolay Toscano</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>JAPON CHILLOGALLO</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>2026-10-27 18:34</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>@motopawer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Marcimex</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Lives</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Motopower</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Iván Quijije Cobeña</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>2026-10-27 18:22</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -3198,6 +3348,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3241,3202 +3392,3202 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>CRECOS 9 DE OCTUBRE 2</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>CRECOS ALBORADA</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CRECOS AMBATO</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CRECOS BABAHOYO</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>CRECOS BALZAR</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>CRECOS BOMBOLI SHOPPING</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>CRECOS CALDERON</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>CRECOS CAYAMBE</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>CRECOS CHONE</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>CRECOS CITY MALL</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>CRECOS COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>CRECOS DAULE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL DORADO</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL EMPALME</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>CRECOS EL RECREO</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>CRECOS ESMERALDAS</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>CRECOS GUARANDA</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>CRECOS IBARRA</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>CRECOS ISLA EL RECREO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA PRENSA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>CRECOS LA TRONCAL</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>CRECOS LATACUNGA</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CRECOS MACHALA</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>CRECOS MALL DEL SUR</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>CRECOS NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>CRECOS NARANJITO</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>CRECOS PEDERNALES</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>CRECOS PIAZZA VIA A LA COSTA</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>CRECOS PINAS</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>CRECOS PLAYAS</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTAL SHOPPING</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTETE</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>CRECOS PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CRECOS QUEVEDO</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>CRECOS QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO NORTE</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CRECOS RIOCENTRO SUR</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>CRECOS SAN VICENTE</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANGOLQUI</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTA ROSA</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>CRECOS SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Crecos</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Crecos</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>CRECOS TUMBACO</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>JAPON AMBATO</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>JAPON BABAHOYO</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>JAPON CALDERON</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>JAPON CARAPUNGO</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>JAPON CAYAMBE</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>JAPON CHONE</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>JAPON COMITE DEL PUEBLO</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>JAPON CONDADO SHOPPING</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>JAPON CUENCA</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>JAPON EL QUINCHE</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 1</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>JAPON EL RECREO 2</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>JAPON ESMERALDAS</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>JAPON GUAMANI</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>JAPON IBARRA 1</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>JAPON IBARRA 2</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>JAPON ISLA MALL DEL SOL</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>JAPON LA CONCORDIA</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>JAPON LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>JAPON LA PRENSA</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>JAPON LATACUNGA</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>JAPON LOJA</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>JAPON MACHACHI</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>JAPON MACHALA</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>JAPON MALL DEL NORTE</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>JAPON MALL DEL PACIFICO</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>JAPON MANTA 1</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>JAPON MANTA 2</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>JAPON MILAGRO</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>JAPON NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>JAPON PARQUE CALIFORNIA</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>JAPON PASAJE</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>JAPON PORTOVIEJO 2</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>JAPON QUEVEDO</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>JAPON QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>JAPON RIOBAMBA</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>JAPON SAN ANTONIO</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>JAPON SANGOLQUI</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>JAPON SANTA ROSA</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>JAPON SANTO DOMINGO 1</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>JAPON SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>JAPON SCALA SHOPPING</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>JAPON TUMBACO</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE AMBATO</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE BABAHOYO</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE EL COCA</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE ISLA QUICENTRO SUR</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE LA PRENSA</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE MILAGRO</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE PORTOVIEJO</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE SANTO DOMINGO 2</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE TUMBACO</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Motozone</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>MOTOZONE VENTANAS</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>ORVE ALBORADA</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>ORVE AMBATO</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>ORVE BABAHOYO</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>ORVE BALZAR</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>ORVE CALCETA</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>ORVE CALDERON</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Sin respuestas</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>Orve Hogar</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>ORVE CARAPUNGO</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11